--- a/saving_curve_nsga2.xlsx
+++ b/saving_curve_nsga2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="21" uniqueCount="3">
   <si>
     <t>T_deadline_s</t>
   </si>
@@ -88,2748 +88,2748 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>102.27345190776548</v>
+        <v>129.50824179088957</v>
       </c>
       <c r="B2" s="0"/>
       <c r="C2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>102.57988550545976</v>
+        <v>130.0890881586692</v>
       </c>
       <c r="B3" s="0">
-        <v>9.741842465509432</v>
+        <v>0.30654325255556569</v>
       </c>
       <c r="C3" s="0">
-        <v>0.25811262947489105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>102.88631910315404</v>
+        <v>130.66993452644883</v>
       </c>
       <c r="B4" s="0">
-        <v>12.721907475551019</v>
+        <v>6.4940153317464286</v>
       </c>
       <c r="C4" s="0">
-        <v>0.36532726867420534</v>
+        <v>0.85118293507388954</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>103.1927527008483</v>
+        <v>131.25078089422848</v>
       </c>
       <c r="B5" s="0">
-        <v>14.978979801409496</v>
+        <v>9.2401139584108734</v>
       </c>
       <c r="C5" s="0">
-        <v>0.18651085264462111</v>
+        <v>0.072208750233284436</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>103.49918629854258</v>
+        <v>131.83162726200811</v>
       </c>
       <c r="B6" s="0">
-        <v>16.23219490361705</v>
+        <v>9.1120508722446907</v>
       </c>
       <c r="C6" s="0">
-        <v>0.0077264418678501257</v>
+        <v>0.62236705432419803</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>103.80561989623686</v>
+        <v>132.41247362978774</v>
       </c>
       <c r="B7" s="0">
-        <v>17.337950294863752</v>
+        <v>10.659984782152558</v>
       </c>
       <c r="C7" s="0">
-        <v>0.086625412854791917</v>
+        <v>0.12126559702265481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>104.11205349393114</v>
+        <v>132.99331999756737</v>
       </c>
       <c r="B8" s="0">
-        <v>18.138646361400006</v>
+        <v>10.795219192794811</v>
       </c>
       <c r="C8" s="0">
-        <v>0.70676893464098123</v>
+        <v>0.85675620997698154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>104.41848709162542</v>
+        <v>133.574166365347</v>
       </c>
       <c r="B9" s="0">
-        <v>18.890296786862479</v>
+        <v>9.3561577802586324</v>
       </c>
       <c r="C9" s="0">
-        <v>0.1595079529694742</v>
+        <v>3.3188787819684267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>104.72492068931969</v>
+        <v>134.15501273312665</v>
       </c>
       <c r="B10" s="0">
-        <v>19.620587754483584</v>
+        <v>6.9019316499164818</v>
       </c>
       <c r="C10" s="0">
-        <v>0.31704467637817502</v>
+        <v>5.960817613835582</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>105.03135428701397</v>
+        <v>134.73585910090628</v>
       </c>
       <c r="B11" s="0">
-        <v>20.517778011984554</v>
+        <v>7.3295890037989482</v>
       </c>
       <c r="C11" s="0">
-        <v>0.074308878842905143</v>
+        <v>8.0651323876131027</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>105.33778788470825</v>
+        <v>135.31670546868591</v>
       </c>
       <c r="B12" s="0">
-        <v>20.527684601915571</v>
+        <v>1.2085012937915949</v>
       </c>
       <c r="C12" s="0">
-        <v>0.23692439070164786</v>
+        <v>1.3268969349796087</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>105.64422148240253</v>
+        <v>135.89755183646554</v>
       </c>
       <c r="B13" s="0">
-        <v>20.584944190104253</v>
+        <v>2.7877159367733628</v>
       </c>
       <c r="C13" s="0">
-        <v>0.27236827389909929</v>
+        <v>3.7529886261922361</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>105.95065508009681</v>
+        <v>136.47839820424517</v>
       </c>
       <c r="B14" s="0">
-        <v>20.615485742471105</v>
+        <v>3.8005957949213034</v>
       </c>
       <c r="C14" s="0">
-        <v>0.17741837331945423</v>
+        <v>5.7888916702191313</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>106.25708867779107</v>
+        <v>137.0592445720248</v>
       </c>
       <c r="B15" s="0">
-        <v>20.733298261461954</v>
+        <v>5.2113467755186633</v>
       </c>
       <c r="C15" s="0">
-        <v>0.25369658384512683</v>
+        <v>7.9439463302272611</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>106.56352227548535</v>
+        <v>137.64009093980445</v>
       </c>
       <c r="B16" s="0">
-        <v>19.551419697970367</v>
+        <v>1.8620066057103184</v>
       </c>
       <c r="C16" s="0">
-        <v>0.29953422436668986</v>
+        <v>4.3208966973964733</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>106.86995587317963</v>
+        <v>138.22093730758408</v>
       </c>
       <c r="B17" s="0">
-        <v>19.620428198165321</v>
+        <v>2.088238695903426</v>
       </c>
       <c r="C17" s="0">
-        <v>0.35420085789405464</v>
+        <v>3.1513892245842841</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>107.17638947087391</v>
+        <v>138.80178367536371</v>
       </c>
       <c r="B18" s="0">
-        <v>20.01064864063958</v>
+        <v>2.3583112024469046</v>
       </c>
       <c r="C18" s="0">
-        <v>0.19517633531630449</v>
+        <v>2.4957539103210826</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>107.48282306856819</v>
+        <v>139.38263004314334</v>
       </c>
       <c r="B19" s="0">
-        <v>19.310997273251349</v>
+        <v>3.1155555319947199</v>
       </c>
       <c r="C19" s="0">
-        <v>0.59441723031820293</v>
+        <v>4.8831906429798027</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>107.78925666626247</v>
+        <v>139.96347641092296</v>
       </c>
       <c r="B20" s="0">
-        <v>18.52255318504028</v>
+        <v>1.9511555972228996</v>
       </c>
       <c r="C20" s="0">
-        <v>0.1797362005222701</v>
+        <v>5.4802299194742705</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>108.09569026395674</v>
+        <v>140.54432277870262</v>
       </c>
       <c r="B21" s="0">
-        <v>18.357090161080041</v>
+        <v>3.1170717359970128</v>
       </c>
       <c r="C21" s="0">
-        <v>0.77466512906174689</v>
+        <v>4.4760715616973199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>108.40212386165102</v>
+        <v>141.12516914648225</v>
       </c>
       <c r="B22" s="0">
-        <v>17.210846606294446</v>
+        <v>4.170479159569064</v>
       </c>
       <c r="C22" s="0">
-        <v>0.24505512653444411</v>
+        <v>6.0797524068961541</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>108.7085574593453</v>
+        <v>141.70601551426188</v>
       </c>
       <c r="B23" s="0">
-        <v>16.262707795436974</v>
+        <v>3.9501971907633697</v>
       </c>
       <c r="C23" s="0">
-        <v>0.78567061624994583</v>
+        <v>6.4467563029343253</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>109.01499105703958</v>
+        <v>142.28686188204151</v>
       </c>
       <c r="B24" s="0">
-        <v>17.338168114527477</v>
+        <v>4.1504649838351613</v>
       </c>
       <c r="C24" s="0">
-        <v>0.077599148777857882</v>
+        <v>6.469865406789399</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>109.32142465473385</v>
+        <v>142.86770824982114</v>
       </c>
       <c r="B25" s="0">
-        <v>15.240497017759449</v>
+        <v>4.3302786095995849</v>
       </c>
       <c r="C25" s="0">
-        <v>0.2448422063119812</v>
+        <v>7.3505585813053447</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>109.62785825242813</v>
+        <v>143.44855461760079</v>
       </c>
       <c r="B26" s="0">
-        <v>14.516943232447668</v>
+        <v>4.7649354427910717</v>
       </c>
       <c r="C26" s="0">
-        <v>0.63464271465831412</v>
+        <v>8.9963323162487541</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>109.93429185012241</v>
+        <v>144.02940098538042</v>
       </c>
       <c r="B27" s="0">
-        <v>13.786724385551604</v>
+        <v>4.7087556317919548</v>
       </c>
       <c r="C27" s="0">
-        <v>0.24101430775767543</v>
+        <v>5.8325094567318683</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>110.24072544781669</v>
+        <v>144.61024735316005</v>
       </c>
       <c r="B28" s="0">
-        <v>13.793685717449279</v>
+        <v>2.9677497639863555</v>
       </c>
       <c r="C28" s="0">
-        <v>0.20021820555669856</v>
+        <v>4.5252173561851157</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>110.54715904551097</v>
+        <v>145.19109372093968</v>
       </c>
       <c r="B29" s="0">
-        <v>12.857141436734942</v>
+        <v>2.2001687903632425</v>
       </c>
       <c r="C29" s="0">
-        <v>0.20700886782351111</v>
+        <v>2.9597907419757696</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>110.85359264320525</v>
+        <v>145.7719400887193</v>
       </c>
       <c r="B30" s="0">
-        <v>12.19331554566423</v>
+        <v>1.8300184041522287</v>
       </c>
       <c r="C30" s="0">
-        <v>0.41804532580771869</v>
+        <v>1.9741441206714252</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>111.16002624089951</v>
+        <v>146.35278645649896</v>
       </c>
       <c r="B31" s="0">
-        <v>11.366135332089261</v>
+        <v>1.290208848600549</v>
       </c>
       <c r="C31" s="0">
-        <v>0.29016559504075051</v>
+        <v>2.5760406889436513</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>111.46645983859379</v>
+        <v>146.93363282427859</v>
       </c>
       <c r="B32" s="0">
-        <v>10.303399837935334</v>
+        <v>-0.22979105126502741</v>
       </c>
       <c r="C32" s="0">
-        <v>1.3678304465400897</v>
+        <v>1.9072508436906464</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>111.77289343628807</v>
+        <v>147.51447919205822</v>
       </c>
       <c r="B33" s="0">
-        <v>11.893451973821985</v>
+        <v>0.50695641918312329</v>
       </c>
       <c r="C33" s="0">
-        <v>1.1804062255871424</v>
+        <v>0.99022449577050031</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>112.07932703398235</v>
+        <v>148.09532555983785</v>
       </c>
       <c r="B34" s="0">
-        <v>11.103265476949172</v>
+        <v>0.52557940283640769</v>
       </c>
       <c r="C34" s="0">
-        <v>0.80162559230436459</v>
+        <v>1.71807316427339</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>112.38576063167662</v>
+        <v>148.67617192761747</v>
       </c>
       <c r="B35" s="0">
-        <v>10.206227322042469</v>
+        <v>-0.74619760271361857</v>
       </c>
       <c r="C35" s="0">
-        <v>0.89967969365713085</v>
+        <v>0.33353598327056955</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>112.6921942293709</v>
+        <v>149.25701829539713</v>
       </c>
       <c r="B36" s="0">
-        <v>9.1866167570533293</v>
+        <v>2.1306602128304233</v>
       </c>
       <c r="C36" s="0">
-        <v>0.30002533292254674</v>
+        <v>1.1938169822140696</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>112.99862782706518</v>
+        <v>149.83786466317676</v>
       </c>
       <c r="B37" s="0">
-        <v>8.2727959097438735</v>
+        <v>2.7004394028222189</v>
       </c>
       <c r="C37" s="0">
-        <v>0.084310575162204429</v>
+        <v>3.0953918087073058</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>113.30506142475946</v>
+        <v>150.41871103095639</v>
       </c>
       <c r="B38" s="0">
-        <v>6.6327430511057095</v>
+        <v>-0.11267599661269376</v>
       </c>
       <c r="C38" s="0">
-        <v>0.83602482969167358</v>
+        <v>0.78993621646800938</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>113.61149502245374</v>
+        <v>150.99955739873602</v>
       </c>
       <c r="B39" s="0">
-        <v>5.2749299584803628</v>
+        <v>0.014943022361046221</v>
       </c>
       <c r="C39" s="0">
-        <v>0.5416315403659876</v>
+        <v>1.1387254402844924</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>113.91792862014802</v>
+        <v>151.58040376651565</v>
       </c>
       <c r="B40" s="0">
-        <v>2.9542790698176717</v>
+        <v>0.99699114483872164</v>
       </c>
       <c r="C40" s="0">
-        <v>1.0815927480675689</v>
+        <v>0.31468833010481534</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>114.22436221784228</v>
+        <v>152.1612501342953</v>
       </c>
       <c r="B41" s="0">
-        <v>-0.012864075992203627</v>
+        <v>2.1288965583063741</v>
       </c>
       <c r="C41" s="0">
-        <v>0.51197037584848415</v>
+        <v>3.1247964843836926</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>114.53079581553656</v>
+        <v>152.74209650207493</v>
       </c>
       <c r="B42" s="0">
-        <v>0.80656764437437234</v>
+        <v>5.3988609889166961</v>
       </c>
       <c r="C42" s="0">
-        <v>0.31050702310487488</v>
+        <v>2.4838011613586386</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>114.83722941323084</v>
+        <v>153.32294286985456</v>
       </c>
       <c r="B43" s="0">
-        <v>0.35853369490769649</v>
+        <v>7.2466371524758433</v>
       </c>
       <c r="C43" s="0">
-        <v>0.94412271084422983</v>
+        <v>3.3161315801606905</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>115.14366301092512</v>
+        <v>153.90378923763419</v>
       </c>
       <c r="B44" s="0">
-        <v>0.57788232535313466</v>
+        <v>7.9490254308194253</v>
       </c>
       <c r="C44" s="0">
-        <v>1.2543285189081324</v>
+        <v>2.4911585706096231</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>115.4500966086194</v>
+        <v>154.48463560541382</v>
       </c>
       <c r="B45" s="0">
-        <v>1.1795828168510758</v>
+        <v>7.9490254308194253</v>
       </c>
       <c r="C45" s="0">
-        <v>1.6738139420067144</v>
+        <v>2.4911585706096231</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>115.75653020631367</v>
+        <v>155.06548197319347</v>
       </c>
       <c r="B46" s="0">
-        <v>2.3592017582860301</v>
+        <v>2.4701328001770619</v>
       </c>
       <c r="C46" s="0">
-        <v>1.708010240179604</v>
+        <v>10.239482835650058</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>116.06296380400795</v>
+        <v>155.6463283409731</v>
       </c>
       <c r="B47" s="0">
-        <v>-0.13837733586925782</v>
+        <v>5.1268274220431085</v>
       </c>
       <c r="C47" s="0">
-        <v>1.8240999878743134</v>
+        <v>13.996616400976681</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>116.36939740170223</v>
+        <v>156.22717470875273</v>
       </c>
       <c r="B48" s="0">
-        <v>-0.52868463332869131</v>
+        <v>3.4926529634217589</v>
       </c>
       <c r="C48" s="0">
-        <v>1.2721221143139927</v>
+        <v>16.307688083642706</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>116.67583099939651</v>
+        <v>156.80802107653236</v>
       </c>
       <c r="B49" s="0">
-        <v>0.42333713310758431</v>
+        <v>2.6266422208405746</v>
       </c>
       <c r="C49" s="0">
-        <v>1.4383875750190929</v>
+        <v>17.53241222096181</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>116.98226459709079</v>
+        <v>157.38886744431198</v>
       </c>
       <c r="B50" s="0">
-        <v>1.0892991978723594</v>
+        <v>4.1532368449131294</v>
       </c>
       <c r="C50" s="0">
-        <v>0.614295691456202</v>
+        <v>19.691343042571074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>117.28869819478506</v>
+        <v>157.96971381209164</v>
       </c>
       <c r="B51" s="0">
-        <v>0.77427918637493709</v>
+        <v>9.3296842220350449</v>
       </c>
       <c r="C51" s="0">
-        <v>1.0949961264346415</v>
+        <v>13.524504890072205</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>117.59513179247934</v>
+        <v>158.55056017987127</v>
       </c>
       <c r="B52" s="0">
-        <v>0.90485356410426343</v>
+        <v>11.905548431708802</v>
       </c>
       <c r="C52" s="0">
-        <v>1.279656182317882</v>
+        <v>14.093550920248438</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>117.90156539017362</v>
+        <v>159.1314065476509</v>
       </c>
       <c r="B53" s="0">
-        <v>1.0695140587127914</v>
+        <v>11.905548431708802</v>
       </c>
       <c r="C53" s="0">
-        <v>2.7683690850916838</v>
+        <v>14.093550920248438</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>118.2079989878679</v>
+        <v>159.71225291543053</v>
       </c>
       <c r="B54" s="0">
-        <v>1.0961841718995462</v>
+        <v>11.315060753702102</v>
       </c>
       <c r="C54" s="0">
-        <v>2.7306518493129497</v>
+        <v>17.540517103034684</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>118.51443258556216</v>
+        <v>160.29309928321015</v>
       </c>
       <c r="B55" s="0">
-        <v>1.3001515702602253</v>
+        <v>11.315060753702102</v>
       </c>
       <c r="C55" s="0">
-        <v>2.4421983882693215</v>
+        <v>17.540517103034684</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>118.82086618325644</v>
+        <v>160.87394565098978</v>
       </c>
       <c r="B56" s="0">
-        <v>2.1243578351984689</v>
+        <v>12.360422776551861</v>
       </c>
       <c r="C56" s="0">
-        <v>3.2012608193868664</v>
+        <v>19.018882253338589</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>119.12729978095072</v>
+        <v>161.45479201876941</v>
       </c>
       <c r="B57" s="0">
-        <v>3.0098488318745908</v>
+        <v>12.360422776551861</v>
       </c>
       <c r="C57" s="0">
-        <v>3.1056503625713177</v>
+        <v>19.018882253338589</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>119.433733378645</v>
+        <v>162.03563838654907</v>
       </c>
       <c r="B58" s="0">
-        <v>3.1088307516455753</v>
+        <v>14.829309688205854</v>
       </c>
       <c r="C58" s="0">
-        <v>2.9656687892014655</v>
+        <v>19.805192988459091</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>119.74016697633928</v>
+        <v>162.6164847543287</v>
       </c>
       <c r="B59" s="0">
-        <v>0.33644653633430893</v>
+        <v>10.833738636447347</v>
       </c>
       <c r="C59" s="0">
-        <v>0.95507456820081826</v>
+        <v>25.455783759281303</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>120.04660057403356</v>
+        <v>163.19733112210832</v>
       </c>
       <c r="B60" s="0">
-        <v>-1.2792563119311968</v>
+        <v>10.315111649707184</v>
       </c>
       <c r="C60" s="0">
-        <v>1.3298743125810988</v>
+        <v>27.917368565035762</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>120.35303417172783</v>
+        <v>163.77817748988795</v>
       </c>
       <c r="B61" s="0">
-        <v>0.48245749671288429</v>
+        <v>10.315111649707184</v>
       </c>
       <c r="C61" s="0">
-        <v>0.38489590284925623</v>
+        <v>27.917368565035762</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>120.65946776942211</v>
+        <v>164.35902385766758</v>
       </c>
       <c r="B62" s="0">
-        <v>0.089091968284192968</v>
+        <v>10.315111649707184</v>
       </c>
       <c r="C62" s="0">
-        <v>0.94119876812317083</v>
+        <v>27.917368565035762</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>120.96590136711639</v>
+        <v>164.93987022544724</v>
       </c>
       <c r="B63" s="0">
-        <v>-0.73519681539505499</v>
+        <v>10.315111649707184</v>
       </c>
       <c r="C63" s="0">
-        <v>1.0397253073451955</v>
+        <v>27.917368565035762</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>121.27233496481067</v>
+        <v>165.52071659322687</v>
       </c>
       <c r="B64" s="0">
-        <v>-1.0235817530740796</v>
+        <v>10.315111649707184</v>
       </c>
       <c r="C64" s="0">
-        <v>1.4475631973949919</v>
+        <v>27.917368565035762</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>121.57876856250493</v>
+        <v>166.10156296100649</v>
       </c>
       <c r="B65" s="0">
-        <v>-0.40126210765186365</v>
+        <v>6.5369340770659345</v>
       </c>
       <c r="C65" s="0">
-        <v>2.3276560800823054</v>
+        <v>33.26051852931888</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>121.88520216019921</v>
+        <v>166.68240932878612</v>
       </c>
       <c r="B66" s="0">
-        <v>-0.99104340933539681</v>
+        <v>15.027836137464062</v>
       </c>
       <c r="C66" s="0">
-        <v>3.1617327957572154</v>
+        <v>21.252569678722182</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>122.19163575789349</v>
+        <v>167.26325569656575</v>
       </c>
       <c r="B67" s="0">
-        <v>0.91280475578968046</v>
+        <v>13.80832394234211</v>
       </c>
       <c r="C67" s="0">
-        <v>0.46928489993819977</v>
+        <v>22.977220364543033</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>122.49806935558777</v>
+        <v>167.84410206434541</v>
       </c>
       <c r="B68" s="0">
-        <v>-0.29246912022979338</v>
+        <v>13.80832394234211</v>
       </c>
       <c r="C68" s="0">
-        <v>0.085003799665658006</v>
+        <v>22.977220364543033</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>122.80450295328205</v>
+        <v>168.42494843212503</v>
       </c>
       <c r="B69" s="0">
-        <v>-0.13061209975833177</v>
+        <v>12.52783613746406</v>
       </c>
       <c r="C69" s="0">
-        <v>0.31390419318169871</v>
+        <v>24.788103584654923</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>123.11093655097633</v>
+        <v>169.00579479990466</v>
       </c>
       <c r="B70" s="0">
-        <v>0.59198913802784203</v>
+        <v>12.52783613746406</v>
       </c>
       <c r="C70" s="0">
-        <v>0</v>
+        <v>24.788103584654923</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>123.41737014867061</v>
+        <v>169.58664116768432</v>
       </c>
       <c r="B71" s="0">
-        <v>0.69196351372698262</v>
+        <v>11.181682291310214</v>
       </c>
       <c r="C71" s="0">
-        <v>0.1413851180035077</v>
+        <v>26.6918526109264</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>123.72380374636488</v>
+        <v>170.16748753546392</v>
       </c>
       <c r="B72" s="0">
-        <v>1.1871908451324094</v>
+        <v>9.7646782427272072</v>
       </c>
       <c r="C72" s="0">
-        <v>0.84174232653489778</v>
+        <v>28.695798954370069</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>124.03023734405916</v>
+        <v>170.74833390324358</v>
       </c>
       <c r="B73" s="0">
-        <v>0.71494118730743161</v>
+        <v>9.7646782427272072</v>
       </c>
       <c r="C73" s="0">
-        <v>1.8427287619017165</v>
+        <v>28.695798954370069</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>124.33667094175344</v>
+        <v>171.3291802710232</v>
       </c>
       <c r="B74" s="0">
-        <v>0.88506594863202404</v>
+        <v>14.921825846764669</v>
       </c>
       <c r="C74" s="0">
-        <v>1.6021360171409922</v>
+        <v>21.40249086958038</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>124.64310453944771</v>
+        <v>171.91002663880283</v>
       </c>
       <c r="B75" s="0">
-        <v>0.89497469943356101</v>
+        <v>14.921825846764669</v>
       </c>
       <c r="C75" s="0">
-        <v>1.5881229273712834</v>
+        <v>21.40249086958038</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>124.94953813714199</v>
+        <v>172.49087300658246</v>
       </c>
       <c r="B76" s="0">
-        <v>0.57515697253761489</v>
+        <v>15.642006193471966</v>
       </c>
       <c r="C76" s="0">
-        <v>2.0404134942348651</v>
+        <v>20.384002055912365</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>125.25597173483627</v>
+        <v>173.07171937436209</v>
       </c>
       <c r="B77" s="0">
-        <v>2.667946587389264</v>
+        <v>22.598125996875353</v>
       </c>
       <c r="C77" s="0">
-        <v>3.3828629523456368</v>
+        <v>34.212418765997192</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>125.56240533253055</v>
+        <v>173.65256574214175</v>
       </c>
       <c r="B78" s="0">
-        <v>-0.87865209634358377</v>
+        <v>22.598125996875353</v>
       </c>
       <c r="C78" s="0">
-        <v>0.20135660971895986</v>
+        <v>34.212418765997192</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>125.86883893022483</v>
+        <v>174.23341210992138</v>
       </c>
       <c r="B79" s="0">
-        <v>-0.87865209634358377</v>
+        <v>-3.3091537745960951</v>
       </c>
       <c r="C79" s="0">
-        <v>0.20135660971895986</v>
+        <v>2.4260076510118669</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>126.17527252791911</v>
+        <v>174.814258477701</v>
       </c>
       <c r="B80" s="0">
-        <v>-0.11328200204968358</v>
+        <v>-3.3091537745960951</v>
       </c>
       <c r="C80" s="0">
-        <v>0.77002284203215754</v>
+        <v>2.4260076510118669</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>126.48170612561339</v>
+        <v>175.39510484548063</v>
       </c>
       <c r="B81" s="0">
-        <v>-0.78178753401232637</v>
+        <v>-4.9004355963512021</v>
       </c>
       <c r="C81" s="0">
-        <v>1.7154324318551677</v>
+        <v>4.6764199848957047</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>126.78813972330765</v>
+        <v>175.97595121326026</v>
       </c>
       <c r="B82" s="0">
-        <v>-0.2011250125789058</v>
+        <v>-4.9004355963512021</v>
       </c>
       <c r="C82" s="0">
-        <v>0.89425161888226634</v>
+        <v>4.6764199848957047</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>127.09457332100193</v>
+        <v>176.55679758103992</v>
       </c>
       <c r="B83" s="0">
-        <v>-0.2011250125789058</v>
+        <v>-7.1880608285389283</v>
       </c>
       <c r="C83" s="0">
-        <v>0.89425161888226634</v>
+        <v>5.5579392674590418</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>127.40100691869621</v>
+        <v>177.13764394881955</v>
       </c>
       <c r="B84" s="0">
-        <v>0.22644170288316562</v>
+        <v>-7.1880608285389283</v>
       </c>
       <c r="C84" s="0">
-        <v>1.498922266708046</v>
+        <v>5.5579392674590418</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>127.70744051639049</v>
+        <v>177.71849031659917</v>
       </c>
       <c r="B85" s="0">
-        <v>-0.80918034362282154</v>
+        <v>-4.0272709266347491</v>
       </c>
       <c r="C85" s="0">
-        <v>2.9635130103693932</v>
+        <v>3.6227013919074587</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>128.01387411408476</v>
+        <v>178.2993366843788</v>
       </c>
       <c r="B86" s="0">
-        <v>-0.31452473976407425</v>
+        <v>-4.0272709266347491</v>
       </c>
       <c r="C86" s="0">
-        <v>4.6748229498637599</v>
+        <v>3.6227013919074587</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>128.32030771177904</v>
+        <v>178.88018305215843</v>
       </c>
       <c r="B87" s="0">
-        <v>-0.31976554672336643</v>
+        <v>-7.4948466241892629</v>
       </c>
       <c r="C87" s="0">
-        <v>5.6977359527573208</v>
+        <v>3.7434581049710416</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>128.62674130947332</v>
+        <v>179.46102941993809</v>
       </c>
       <c r="B88" s="0">
-        <v>1.623209587208625</v>
+        <v>-4.4125872819928294</v>
       </c>
       <c r="C88" s="0">
-        <v>2.949954166997018</v>
+        <v>8.1024310694564114</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>128.9331749071676</v>
+        <v>180.04187578771772</v>
       </c>
       <c r="B89" s="0">
-        <v>2.3210416896935446</v>
+        <v>-6.1140235462804888</v>
       </c>
       <c r="C89" s="0">
-        <v>3.936837790590523</v>
+        <v>5.6962368289873906</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>129.23960850486188</v>
+        <v>180.62272215549734</v>
       </c>
       <c r="B90" s="0">
-        <v>2.045444907576762</v>
+        <v>-6.1140235462804888</v>
       </c>
       <c r="C90" s="0">
-        <v>4.7804763117750024</v>
+        <v>5.6962368289873906</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>129.54604210255616</v>
+        <v>181.20356852327697</v>
       </c>
       <c r="B91" s="0">
-        <v>3.149361425362879</v>
+        <v>5.366886280745268</v>
       </c>
       <c r="C91" s="0">
-        <v>4.0104091048820258</v>
+        <v>1.8381670498765843</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>129.85247570025044</v>
+        <v>181.7844148910566</v>
       </c>
       <c r="B92" s="0">
-        <v>3.5138360812019651</v>
+        <v>5.366886280745268</v>
       </c>
       <c r="C92" s="0">
-        <v>3.9989540037712939</v>
+        <v>1.8381670498765843</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>130.15890929794472</v>
+        <v>182.36526125883626</v>
       </c>
       <c r="B93" s="0">
-        <v>2.8733583879908844</v>
+        <v>-3.3713690564834748</v>
       </c>
       <c r="C93" s="0">
-        <v>4.904726243907839</v>
+        <v>0.46999216534533006</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>130.46534289563897</v>
+        <v>182.94610762661588</v>
       </c>
       <c r="B94" s="0">
-        <v>3.6734102970147471</v>
+        <v>-3.3713690564834748</v>
       </c>
       <c r="C94" s="0">
-        <v>5.1949866621992342</v>
+        <v>0.46999216534533006</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>130.77177649333325</v>
+        <v>183.52695399439551</v>
       </c>
       <c r="B95" s="0">
-        <v>3.8371157393068387</v>
+        <v>-5.3656710507854708</v>
       </c>
       <c r="C95" s="0">
-        <v>5.4265011189229968</v>
+        <v>3.2903610931549236</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>131.07821009102753</v>
+        <v>184.10780036217514</v>
       </c>
       <c r="B96" s="0">
-        <v>3.8371157393068387</v>
+        <v>-5.3656710507854708</v>
       </c>
       <c r="C96" s="0">
-        <v>5.4265011189229968</v>
+        <v>3.2903610931549236</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>131.38464368872181</v>
+        <v>184.68864672995477</v>
       </c>
       <c r="B97" s="0">
-        <v>0.75046913649977354</v>
+        <v>-5.3656710507854708</v>
       </c>
       <c r="C97" s="0">
-        <v>1.0613236309804053</v>
+        <v>3.2903610931549236</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>131.69107728641609</v>
+        <v>185.26949309773443</v>
       </c>
       <c r="B98" s="0">
-        <v>0.75046913649977354</v>
+        <v>-5.6410785810021551</v>
       </c>
       <c r="C98" s="0">
-        <v>1.0613236309804053</v>
+        <v>7.9776898356656218</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>131.99751088411037</v>
+        <v>185.85033946551405</v>
       </c>
       <c r="B99" s="0">
-        <v>0.93711966529976976</v>
+        <v>-0.64355707950399599</v>
       </c>
       <c r="C99" s="0">
-        <v>0.79735992172734071</v>
+        <v>0.91012714999577138</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>132.30394448180465</v>
+        <v>186.43118583329368</v>
       </c>
       <c r="B100" s="0">
-        <v>1.0354923001544361</v>
+        <v>-2.7268904128373253</v>
       </c>
       <c r="C100" s="0">
-        <v>0.6582400073494955</v>
+        <v>2.0361511049481713</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>132.61037807949893</v>
+        <v>187.01203220107331</v>
       </c>
       <c r="B101" s="0">
-        <v>1.4133671151844363</v>
+        <v>-2.7268904128373253</v>
       </c>
       <c r="C101" s="0">
-        <v>1.1926356956441464</v>
+        <v>2.0361511049481713</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>132.91681167719321</v>
+        <v>187.59287856885294</v>
       </c>
       <c r="B102" s="0">
-        <v>-0.095626173615052545</v>
+        <v>-2.0198311820662602</v>
       </c>
       <c r="C102" s="0">
-        <v>0.94140307890607111</v>
+        <v>3.0360838585057</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0">
-        <v>133.22324527488746</v>
+        <v>188.1737249366326</v>
       </c>
       <c r="B103" s="0">
-        <v>-0.061925085304723737</v>
+        <v>-6.3621353428256437</v>
       </c>
       <c r="C103" s="0">
-        <v>0.89374254275087073</v>
+        <v>3.1048615775893409</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0">
-        <v>133.52967887258177</v>
+        <v>188.75457130441222</v>
       </c>
       <c r="B104" s="0">
-        <v>-0.061925085304723737</v>
+        <v>-6.3621353428256437</v>
       </c>
       <c r="C104" s="0">
-        <v>0.89374254275087073</v>
+        <v>3.1048615775893409</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0">
-        <v>133.83611247027602</v>
+        <v>189.33541767219185</v>
       </c>
       <c r="B105" s="0">
-        <v>-2.0652660666994862</v>
+        <v>-8.8293536159843882</v>
       </c>
       <c r="C105" s="0">
-        <v>1.9394094431954285</v>
+        <v>6.5940351208251631</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0">
-        <v>134.1425460679703</v>
+        <v>189.91626403997148</v>
       </c>
       <c r="B106" s="0">
-        <v>-0.64179278479761925</v>
+        <v>-13.564202100832883</v>
       </c>
       <c r="C106" s="0">
-        <v>0.073685777745931685</v>
+        <v>0.1020518222292796</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0">
-        <v>134.44897966566458</v>
+        <v>190.49711040775111</v>
       </c>
       <c r="B107" s="0">
-        <v>0.38930637180270028</v>
+        <v>-6.3704309755366788</v>
       </c>
       <c r="C107" s="0">
-        <v>1.3845086336696999</v>
+        <v>10.275580512231134</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0">
-        <v>134.75541326335886</v>
+        <v>191.07795677553077</v>
       </c>
       <c r="B108" s="0">
-        <v>-0.015607938742952743</v>
+        <v>-8.730061887791674</v>
       </c>
       <c r="C108" s="0">
-        <v>1.4764966325418416</v>
+        <v>6.9385584739253208</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0">
-        <v>135.06184686105314</v>
+        <v>191.65880314331037</v>
       </c>
       <c r="B109" s="0">
-        <v>0.72770081151513155</v>
+        <v>-11.435689593419374</v>
       </c>
       <c r="C109" s="0">
-        <v>0.42529931689626288</v>
+        <v>10.764893869956413</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0">
-        <v>135.36828045874742</v>
+        <v>192.23964951109002</v>
       </c>
       <c r="B110" s="0">
-        <v>0.72770081151513155</v>
+        <v>-11.435689593419374</v>
       </c>
       <c r="C110" s="0">
-        <v>0.42529931689626288</v>
+        <v>10.764893869956413</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0">
-        <v>135.6747140564417</v>
+        <v>192.82049587886965</v>
       </c>
       <c r="B111" s="0">
-        <v>0.72770081151513155</v>
+        <v>-14.031283596899861</v>
       </c>
       <c r="C111" s="0">
-        <v>0.42529931689626288</v>
+        <v>7.0941696278200297</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0">
-        <v>135.98114765413598</v>
+        <v>193.40134224664928</v>
       </c>
       <c r="B112" s="0">
-        <v>1.5687070624207338</v>
+        <v>-14.031283596899861</v>
       </c>
       <c r="C112" s="0">
-        <v>1.2691124515296202</v>
+        <v>7.0941696278200297</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0">
-        <v>136.28758125183026</v>
+        <v>193.98218861442894</v>
       </c>
       <c r="B113" s="0">
-        <v>1.5687070624207338</v>
+        <v>-14.031283596899861</v>
       </c>
       <c r="C113" s="0">
-        <v>1.2691124515296202</v>
+        <v>7.0941696278200297</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0">
-        <v>136.59401484952451</v>
+        <v>194.56303498220854</v>
       </c>
       <c r="B114" s="0">
-        <v>1.5687070624207338</v>
+        <v>-16.900098021799355</v>
       </c>
       <c r="C114" s="0">
-        <v>1.2691124515296202</v>
+        <v>3.0370533601955945</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0">
-        <v>136.90044844721882</v>
+        <v>195.14388134998819</v>
       </c>
       <c r="B115" s="0">
-        <v>2.1911184361305618</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C115" s="0">
-        <v>0.38888984545391286</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0">
-        <v>137.20688204491307</v>
+        <v>195.72472771776782</v>
       </c>
       <c r="B116" s="0">
-        <v>2.1911184361305618</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C116" s="0">
-        <v>0.38888984545391286</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0">
-        <v>137.51331564260735</v>
+        <v>196.30557408554745</v>
       </c>
       <c r="B117" s="0">
-        <v>0.39119874311026992</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C117" s="0">
-        <v>4.2796492453609005</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0">
-        <v>137.81974924030163</v>
+        <v>196.8864204533271</v>
       </c>
       <c r="B118" s="0">
-        <v>0.58840958315291481</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C118" s="0">
-        <v>4.5585474899962</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0">
-        <v>138.12618283799591</v>
+        <v>197.46726682110671</v>
       </c>
       <c r="B119" s="0">
-        <v>0.58840958315291481</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C119" s="0">
-        <v>4.5585474899962</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0">
-        <v>138.43261643569019</v>
+        <v>198.04811318888636</v>
       </c>
       <c r="B120" s="0">
-        <v>0.58840958315291481</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C120" s="0">
-        <v>4.5585474899962</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0">
-        <v>138.73905003338447</v>
+        <v>198.62895955666599</v>
       </c>
       <c r="B121" s="0">
-        <v>0.45702527139432947</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C121" s="0">
-        <v>7.0009054604081786</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0">
-        <v>139.04548363107875</v>
+        <v>199.20980592444562</v>
       </c>
       <c r="B122" s="0">
-        <v>0.45702527139432947</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C122" s="0">
-        <v>7.0009054604081786</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0">
-        <v>139.35191722877301</v>
+        <v>199.79065229222528</v>
       </c>
       <c r="B123" s="0">
-        <v>0.45702527139432947</v>
+        <v>-9.5238095238095255</v>
       </c>
       <c r="C123" s="0">
-        <v>7.0009054604081786</v>
+        <v>13.46870059402948</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0">
-        <v>139.65835082646731</v>
+        <v>200.37149866000487</v>
       </c>
       <c r="B124" s="0">
-        <v>0.45702527139432947</v>
+        <v>8.1310481698034405</v>
       </c>
       <c r="C124" s="0">
-        <v>7.0009054604081786</v>
+        <v>11.499038598044958</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0">
-        <v>139.96478442416157</v>
+        <v>200.95234502778453</v>
       </c>
       <c r="B125" s="0">
-        <v>1.1638715703265419</v>
+        <v>8.1310481698034405</v>
       </c>
       <c r="C125" s="0">
-        <v>8.0005370828713396</v>
+        <v>11.499038598044958</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0">
-        <v>140.27121802185584</v>
+        <v>201.53319139556416</v>
       </c>
       <c r="B126" s="0">
-        <v>1.286298648673327</v>
+        <v>8.1310481698034405</v>
       </c>
       <c r="C126" s="0">
-        <v>8.1736751174710758</v>
+        <v>11.499038598044958</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0">
-        <v>140.57765161955013</v>
+        <v>202.11403776334379</v>
       </c>
       <c r="B127" s="0">
-        <v>1.286298648673327</v>
+        <v>-5.2022851635298846</v>
       </c>
       <c r="C127" s="0">
-        <v>8.1736751174710758</v>
+        <v>30.355219429686212</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0">
-        <v>140.8840852172444</v>
+        <v>202.69488413112342</v>
       </c>
       <c r="B128" s="0">
-        <v>1.286298648673327</v>
+        <v>-5.2022851635298846</v>
       </c>
       <c r="C128" s="0">
-        <v>8.1736751174710758</v>
+        <v>30.355219429686212</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0">
-        <v>141.19051881493869</v>
+        <v>203.27573049890304</v>
       </c>
       <c r="B129" s="0">
-        <v>1.286298648673327</v>
+        <v>-5.2022851635298846</v>
       </c>
       <c r="C129" s="0">
-        <v>8.1736751174710758</v>
+        <v>30.355219429686212</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0">
-        <v>141.49695241263296</v>
+        <v>203.8565768666827</v>
       </c>
       <c r="B130" s="0">
-        <v>1.286298648673327</v>
+        <v>-5.2022851635298846</v>
       </c>
       <c r="C130" s="0">
-        <v>8.1736751174710758</v>
+        <v>30.355219429686212</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0">
-        <v>141.80338601032725</v>
+        <v>204.4374232344623</v>
       </c>
       <c r="B131" s="0">
-        <v>0.1091198452366271</v>
+        <v>-9.7260946873394243</v>
       </c>
       <c r="C131" s="0">
-        <v>12.141822698957295</v>
+        <v>36.752852211850232</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0">
-        <v>142.10981960802152</v>
+        <v>205.01826960224196</v>
       </c>
       <c r="B132" s="0">
-        <v>0.1091198452366271</v>
+        <v>-9.7260946873394243</v>
       </c>
       <c r="C132" s="0">
-        <v>12.141822698957295</v>
+        <v>36.752852211850232</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0">
-        <v>142.41625320571581</v>
+        <v>205.59911597002159</v>
       </c>
       <c r="B133" s="0">
-        <v>0.1091198452366271</v>
+        <v>-9.7260946873394243</v>
       </c>
       <c r="C133" s="0">
-        <v>12.141822698957295</v>
+        <v>36.752852211850232</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0">
-        <v>142.72268680341006</v>
+        <v>206.17996233780122</v>
       </c>
       <c r="B134" s="0">
-        <v>-0.41886388916624107</v>
+        <v>12.958270992919239</v>
       </c>
       <c r="C134" s="0">
-        <v>12.888504456862224</v>
+        <v>28.512798854731369</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0">
-        <v>143.02912040110434</v>
+        <v>206.76080870558087</v>
       </c>
       <c r="B135" s="0">
-        <v>0.34379948344405431</v>
+        <v>12.958270992919239</v>
       </c>
       <c r="C135" s="0">
-        <v>13.96707334193291</v>
+        <v>28.512798854731369</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0">
-        <v>143.33555399879862</v>
+        <v>207.3416550733605</v>
       </c>
       <c r="B136" s="0">
-        <v>0.34379948344405431</v>
+        <v>12.958270992919239</v>
       </c>
       <c r="C136" s="0">
-        <v>13.96707334193291</v>
+        <v>28.512798854731369</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0">
-        <v>143.6419875964929</v>
+        <v>207.92250144114013</v>
       </c>
       <c r="B137" s="0">
-        <v>4.9018885907472241</v>
+        <v>12.958270992919239</v>
       </c>
       <c r="C137" s="0">
-        <v>7.5209619078796939</v>
+        <v>28.512798854731369</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0">
-        <v>143.94842119418718</v>
+        <v>208.50334780891978</v>
       </c>
       <c r="B138" s="0">
-        <v>5.1321869692811388</v>
+        <v>12.958270992919239</v>
       </c>
       <c r="C138" s="0">
-        <v>7.8466529981948883</v>
+        <v>28.512798854731369</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0">
-        <v>144.25485479188146</v>
+        <v>209.08419417669939</v>
       </c>
       <c r="B139" s="0">
-        <v>5.1321869692811388</v>
+        <v>12.958270992919239</v>
       </c>
       <c r="C139" s="0">
-        <v>7.8466529981948883</v>
+        <v>28.512798854731369</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0">
-        <v>144.56128838957574</v>
+        <v>209.66504054447904</v>
       </c>
       <c r="B140" s="0">
-        <v>5.8365965788819061</v>
+        <v>12.095727593666766</v>
       </c>
       <c r="C140" s="0">
-        <v>6.8504673748315455</v>
+        <v>29.73261942808961</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0">
-        <v>144.86772198727002</v>
+        <v>210.24588691225867</v>
       </c>
       <c r="B141" s="0">
-        <v>5.9409930363460735</v>
+        <v>12.095727593666766</v>
       </c>
       <c r="C141" s="0">
-        <v>6.9981062608410776</v>
+        <v>29.73261942808961</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0">
-        <v>145.1741555849643</v>
+        <v>210.8267332800383</v>
       </c>
       <c r="B142" s="0">
-        <v>6.403800114188039</v>
+        <v>12.095727593666766</v>
       </c>
       <c r="C142" s="0">
-        <v>7.6526143070874459</v>
+        <v>29.73261942808961</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0">
-        <v>145.48058918265858</v>
+        <v>211.40757964781795</v>
       </c>
       <c r="B143" s="0">
-        <v>-0.071594348839859379</v>
+        <v>12.095727593666766</v>
       </c>
       <c r="C143" s="0">
-        <v>1.6067925604453073</v>
+        <v>29.73261942808961</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0">
-        <v>145.78702278035286</v>
+        <v>211.98842601559755</v>
       </c>
       <c r="B144" s="0">
-        <v>-0.071594348839859379</v>
+        <v>7.1444362651952034</v>
       </c>
       <c r="C144" s="0">
-        <v>1.6067925604453073</v>
+        <v>36.734802776074389</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0">
-        <v>146.09345637804711</v>
+        <v>212.56927238337721</v>
       </c>
       <c r="B145" s="0">
-        <v>-0.071594348839859379</v>
+        <v>9.2863030089165886</v>
       </c>
       <c r="C145" s="0">
-        <v>1.6067925604453073</v>
+        <v>35.952401827880557</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0">
-        <v>146.39988997574142</v>
+        <v>213.15011875115684</v>
       </c>
       <c r="B146" s="0">
-        <v>-1.5695192683143615</v>
+        <v>9.2863030089165886</v>
       </c>
       <c r="C146" s="0">
-        <v>0.59105101826489426</v>
+        <v>35.952401827880557</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0">
-        <v>146.70632357343567</v>
+        <v>213.73096511893647</v>
       </c>
       <c r="B147" s="0">
-        <v>-1.0110545762892036</v>
+        <v>9.2863030089165886</v>
       </c>
       <c r="C147" s="0">
-        <v>0.19873732330359775</v>
+        <v>35.952401827880557</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0">
-        <v>147.01275717112995</v>
+        <v>214.3118114867161</v>
       </c>
       <c r="B148" s="0">
-        <v>-1.0110545762892036</v>
+        <v>10.814982265305092</v>
       </c>
       <c r="C148" s="0">
-        <v>0.19873732330359775</v>
+        <v>38.114280764783601</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0">
-        <v>147.31919076882423</v>
+        <v>214.89265785449572</v>
       </c>
       <c r="B149" s="0">
-        <v>-1.4132514944963135</v>
+        <v>22.90053908951975</v>
       </c>
       <c r="C149" s="0">
-        <v>0.72972087791924001</v>
+        <v>34.073570331404277</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0">
-        <v>147.62562436651851</v>
+        <v>215.47350422227538</v>
       </c>
       <c r="B150" s="0">
-        <v>-1.4132514944963135</v>
+        <v>17.840883411967109</v>
       </c>
       <c r="C150" s="0">
-        <v>0.72972087791924001</v>
+        <v>41.229004011537249</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0">
-        <v>147.93205796421279</v>
+        <v>216.05435059005498</v>
       </c>
       <c r="B151" s="0">
-        <v>-1.1406815812240718</v>
+        <v>17.840883411967109</v>
       </c>
       <c r="C151" s="0">
-        <v>1.1151929459637022</v>
+        <v>41.229004011537249</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0">
-        <v>148.23849156190707</v>
+        <v>216.63519695783464</v>
       </c>
       <c r="B152" s="0">
-        <v>-1.1406815812240718</v>
+        <v>17.840883411967109</v>
       </c>
       <c r="C152" s="0">
-        <v>1.1151929459637022</v>
+        <v>41.229004011537249</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0">
-        <v>148.54492515960135</v>
+        <v>217.21604332561427</v>
       </c>
       <c r="B153" s="0">
-        <v>-1.9131962444910471</v>
+        <v>17.840883411967102</v>
       </c>
       <c r="C153" s="0">
-        <v>0.8109729045941515</v>
+        <v>41.229004011537256</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0">
-        <v>148.8513587572956</v>
+        <v>217.79688969339389</v>
       </c>
       <c r="B154" s="0">
-        <v>-1.7069781555177761</v>
+        <v>17.840883411967102</v>
       </c>
       <c r="C154" s="0">
-        <v>0.51933648636148999</v>
+        <v>41.229004011537256</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0">
-        <v>149.15779235498991</v>
+        <v>218.37773606117355</v>
       </c>
       <c r="B155" s="0">
-        <v>-1.7069781555177761</v>
+        <v>11.656859806069424</v>
       </c>
       <c r="C155" s="0">
-        <v>0.51933648636148999</v>
+        <v>49.974534065033133</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0">
-        <v>149.46422595268416</v>
+        <v>218.95858242895315</v>
       </c>
       <c r="B156" s="0">
-        <v>-1.3956102322291999</v>
+        <v>11.656859806069424</v>
       </c>
       <c r="C156" s="0">
-        <v>0.95967722636413988</v>
+        <v>49.974534065033133</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0">
-        <v>149.77065955037844</v>
+        <v>219.53942879673281</v>
       </c>
       <c r="B157" s="0">
-        <v>-1.257501475746925</v>
+        <v>11.656859806069424</v>
       </c>
       <c r="C157" s="0">
-        <v>0.76436194986442341</v>
+        <v>49.974534065033133</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0">
-        <v>150.07709314807272</v>
+        <v>220.12027516451244</v>
       </c>
       <c r="B158" s="0">
-        <v>-1.1407162216895064</v>
+        <v>11.656859806069424</v>
       </c>
       <c r="C158" s="0">
-        <v>0.59920265969123454</v>
+        <v>49.974534065033133</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0">
-        <v>150.383526745767</v>
+        <v>220.70112153229206</v>
       </c>
       <c r="B159" s="0">
-        <v>-1.1407162216895064</v>
+        <v>11.656859806069415</v>
       </c>
       <c r="C159" s="0">
-        <v>0.59920265969123454</v>
+        <v>49.97453406503314</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0">
-        <v>150.68996034346128</v>
+        <v>221.28196790007172</v>
       </c>
       <c r="B160" s="0">
-        <v>-1.1407162216895064</v>
+        <v>11.656859806069415</v>
       </c>
       <c r="C160" s="0">
-        <v>0.59920265969123454</v>
+        <v>49.97453406503314</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0">
-        <v>150.99639394115556</v>
+        <v>221.86281426785132</v>
       </c>
       <c r="B161" s="0">
-        <v>-2.7956784377128225</v>
+        <v>11.656859806069415</v>
       </c>
       <c r="C161" s="0">
-        <v>1.7412673514239709</v>
+        <v>49.97453406503314</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0">
-        <v>151.30282753884984</v>
+        <v>222.44366063563098</v>
       </c>
       <c r="B162" s="0">
-        <v>-2.7956784377128225</v>
+        <v>11.656859806069415</v>
       </c>
       <c r="C162" s="0">
-        <v>1.7412673514239709</v>
+        <v>49.97453406503314</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0">
-        <v>151.60926113654412</v>
+        <v>223.0245070034106</v>
       </c>
       <c r="B163" s="0">
-        <v>-2.2905025325315247</v>
+        <v>11.656859806069415</v>
       </c>
       <c r="C163" s="0">
-        <v>1.5719920075263984</v>
+        <v>49.97453406503314</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0">
-        <v>151.9156947342384</v>
+        <v>223.60535337119023</v>
       </c>
       <c r="B164" s="0">
-        <v>-2.2905025325315247</v>
+        <v>3.9268302986973254</v>
       </c>
       <c r="C164" s="0">
-        <v>1.5719920075263984</v>
+        <v>60.906446631902966</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0">
-        <v>152.22212833193265</v>
+        <v>224.18619973896989</v>
       </c>
       <c r="B165" s="0">
-        <v>-3.9806578898658609</v>
+        <v>3.9268302986973254</v>
       </c>
       <c r="C165" s="0">
-        <v>0.81824862133336418</v>
+        <v>60.906446631902966</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0">
-        <v>152.52856192962693</v>
+        <v>224.76704610674952</v>
       </c>
       <c r="B166" s="0">
-        <v>-3.9806578898658609</v>
+        <v>3.9268302986973254</v>
       </c>
       <c r="C166" s="0">
-        <v>0.81824862133336418</v>
+        <v>60.906446631902966</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0">
-        <v>152.83499552732121</v>
+        <v>225.34789247452915</v>
       </c>
       <c r="B167" s="0">
-        <v>-3.9806578898658609</v>
+        <v>3.9268302986973254</v>
       </c>
       <c r="C167" s="0">
-        <v>0.81824862133336418</v>
+        <v>60.906446631902966</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0">
-        <v>153.14142912501549</v>
+        <v>225.92873884230877</v>
       </c>
       <c r="B168" s="0">
-        <v>-3.9806578898658609</v>
+        <v>3.9268302986973254</v>
       </c>
       <c r="C168" s="0">
-        <v>0.81824862133336418</v>
+        <v>60.906446631902966</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0">
-        <v>153.44786272270977</v>
+        <v>226.5095852100884</v>
       </c>
       <c r="B169" s="0">
-        <v>-3.5629590373637807</v>
+        <v>3.9268302986973254</v>
       </c>
       <c r="C169" s="0">
-        <v>1.4089640035294842</v>
+        <v>60.906446631902966</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0">
-        <v>153.75429632040405</v>
+        <v>227.09043157786806</v>
       </c>
       <c r="B170" s="0">
-        <v>-3.5629590373637807</v>
+        <v>3.9268302986973254</v>
       </c>
       <c r="C170" s="0">
-        <v>1.4089640035294842</v>
+        <v>60.906446631902966</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0">
-        <v>154.06072991809833</v>
+        <v>227.67127794564766</v>
       </c>
       <c r="B171" s="0">
-        <v>-3.5629590373637807</v>
+        <v>16.070853742975693</v>
       </c>
       <c r="C171" s="0">
-        <v>1.4089640035294842</v>
+        <v>43.732203975227669</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0">
-        <v>154.36716351579261</v>
+        <v>228.25212431342732</v>
       </c>
       <c r="B172" s="0">
-        <v>-3.5629590373637807</v>
+        <v>16.070853742975693</v>
       </c>
       <c r="C172" s="0">
-        <v>1.4089640035294842</v>
+        <v>43.732203975227669</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0">
-        <v>154.67359711348689</v>
+        <v>228.83297068120694</v>
       </c>
       <c r="B173" s="0">
-        <v>-3.5629590373637807</v>
+        <v>16.070853742975693</v>
       </c>
       <c r="C173" s="0">
-        <v>1.4089640035294842</v>
+        <v>43.732203975227669</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0">
-        <v>154.98003071118117</v>
+        <v>229.41381704898657</v>
       </c>
       <c r="B174" s="0">
-        <v>-3.5629590373637807</v>
+        <v>20.710786903514283</v>
       </c>
       <c r="C174" s="0">
-        <v>1.4089640035294842</v>
+        <v>50.294060379366002</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0">
-        <v>155.28646430887545</v>
+        <v>229.99466341676623</v>
       </c>
       <c r="B175" s="0">
-        <v>-3.3602495734754978</v>
+        <v>20.710786903514283</v>
       </c>
       <c r="C175" s="0">
-        <v>1.1222895304772946</v>
+        <v>50.294060379366002</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0">
-        <v>155.5928979065697</v>
+        <v>230.57550978454583</v>
       </c>
       <c r="B176" s="0">
-        <v>-3.3602495734754978</v>
+        <v>20.710786903514283</v>
       </c>
       <c r="C176" s="0">
-        <v>1.1222895304772946</v>
+        <v>50.294060379366002</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0">
-        <v>155.89933150426401</v>
+        <v>231.15635615232549</v>
       </c>
       <c r="B177" s="0">
-        <v>-3.2050180531519992</v>
+        <v>29.837907985717607</v>
       </c>
       <c r="C177" s="0">
-        <v>0.90275900912800855</v>
+        <v>45.988421102026727</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0">
-        <v>156.20576510195826</v>
+        <v>231.73720252010512</v>
       </c>
       <c r="B178" s="0">
-        <v>-2.8281443087999358</v>
+        <v>29.837907985717607</v>
       </c>
       <c r="C178" s="0">
-        <v>0.36977904856298993</v>
+        <v>45.988421102026727</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0">
-        <v>156.51219869965254</v>
+        <v>232.31804888788474</v>
       </c>
       <c r="B179" s="0">
-        <v>-2.8281443087999358</v>
+        <v>29.837907985717607</v>
       </c>
       <c r="C179" s="0">
-        <v>0.36977904856298993</v>
+        <v>45.988421102026727</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0">
-        <v>156.81863229734682</v>
+        <v>232.8988952556644</v>
       </c>
       <c r="B180" s="0">
-        <v>-7.038048568206726</v>
+        <v>29.837907985717607</v>
       </c>
       <c r="C180" s="0">
-        <v>0.45780321236979338</v>
+        <v>45.988421102026727</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0">
-        <v>157.1250658950411</v>
+        <v>233.479741623444</v>
       </c>
       <c r="B181" s="0">
-        <v>-6.8300928528547331</v>
+        <v>29.837907985717607</v>
       </c>
       <c r="C181" s="0">
-        <v>0.75189700539357984</v>
+        <v>45.988421102026727</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0">
-        <v>157.43149949273538</v>
+        <v>234.06058799122366</v>
       </c>
       <c r="B182" s="0">
-        <v>-5.972535615267125</v>
+        <v>29.837907985717607</v>
       </c>
       <c r="C182" s="0">
-        <v>0.00023287215377855742</v>
+        <v>45.988421102026727</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0">
-        <v>157.73793309042964</v>
+        <v>234.64143435900329</v>
       </c>
       <c r="B183" s="0">
-        <v>-5.972535615267125</v>
+        <v>31.409961930094021</v>
       </c>
       <c r="C183" s="0">
-        <v>0.00023287215377855742</v>
+        <v>48.211641110945976</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0">
-        <v>158.04436668812394</v>
+        <v>235.22228072678291</v>
       </c>
       <c r="B184" s="0">
-        <v>-5.9256709669530876</v>
+        <v>31.409961930094021</v>
       </c>
       <c r="C184" s="0">
-        <v>0.066509493395336225</v>
+        <v>48.211641110945976</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0">
-        <v>158.3508002858182</v>
+        <v>235.80312709456254</v>
       </c>
       <c r="B185" s="0">
-        <v>-5.9256709669530876</v>
+        <v>31.409961930094021</v>
       </c>
       <c r="C185" s="0">
-        <v>0.066509493395336225</v>
+        <v>48.211641110945976</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0">
-        <v>158.65723388351248</v>
+        <v>236.38397346234217</v>
       </c>
       <c r="B186" s="0">
-        <v>-6.3969417052143616</v>
+        <v>31.409961930094021</v>
       </c>
       <c r="C186" s="0">
-        <v>1.1981058848025068</v>
+        <v>48.211641110945976</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0">
-        <v>158.96366748120676</v>
+        <v>236.96481983012183</v>
       </c>
       <c r="B187" s="0">
-        <v>-6.3969417052143616</v>
+        <v>31.409961930094021</v>
       </c>
       <c r="C187" s="0">
-        <v>1.1981058848025068</v>
+        <v>48.211641110945976</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0">
-        <v>159.27010107890104</v>
+        <v>237.54566619790143</v>
       </c>
       <c r="B188" s="0">
-        <v>-6.3969417052143616</v>
+        <v>37.47182851184057</v>
       </c>
       <c r="C188" s="0">
-        <v>1.1981058848025068</v>
+        <v>39.638867177743769</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0">
-        <v>159.57653467659532</v>
+        <v>238.12651256568108</v>
       </c>
       <c r="B189" s="0">
-        <v>-6.3969417052143616</v>
+        <v>37.47182851184057</v>
       </c>
       <c r="C189" s="0">
-        <v>1.1981058848025068</v>
+        <v>39.638867177743769</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0">
-        <v>159.8829682742896</v>
+        <v>238.70735893346071</v>
       </c>
       <c r="B190" s="0">
-        <v>-6.3969417052143616</v>
+        <v>37.47182851184057</v>
       </c>
       <c r="C190" s="0">
-        <v>1.1981058848025068</v>
+        <v>39.638867177743769</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0">
-        <v>160.18940187198388</v>
+        <v>239.28820530124034</v>
       </c>
       <c r="B191" s="0">
-        <v>-6.3969417052143616</v>
+        <v>37.47182851184057</v>
       </c>
       <c r="C191" s="0">
-        <v>1.1981058848025068</v>
+        <v>39.638867177743769</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0">
-        <v>160.49583546967816</v>
+        <v>239.86905166902</v>
       </c>
       <c r="B192" s="0">
-        <v>-6.3969417052143616</v>
+        <v>37.47182851184057</v>
       </c>
       <c r="C192" s="0">
-        <v>1.1981058848025068</v>
+        <v>39.638867177743769</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0">
-        <v>160.80226906737244</v>
+        <v>240.4498980367996</v>
       </c>
       <c r="B193" s="0">
-        <v>-8.3376326517716066</v>
+        <v>40.143512663211269</v>
       </c>
       <c r="C193" s="0">
-        <v>0.3063544509794216</v>
+        <v>37.948109283427847</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0">
-        <v>161.10870266506672</v>
+        <v>241.03074440457925</v>
       </c>
       <c r="B194" s="0">
-        <v>-8.3376326517716066</v>
+        <v>40.143512663211269</v>
       </c>
       <c r="C194" s="0">
-        <v>0.3063544509794216</v>
+        <v>37.948109283427847</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0">
-        <v>161.415136262761</v>
+        <v>241.61159077235891</v>
       </c>
       <c r="B195" s="0">
-        <v>-8.3376326517716066</v>
+        <v>40.143512663211269</v>
       </c>
       <c r="C195" s="0">
-        <v>0.3063544509794216</v>
+        <v>37.948109283427847</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0">
-        <v>161.72156986045525</v>
+        <v>242.19243714013851</v>
       </c>
       <c r="B196" s="0">
-        <v>-8.3376326517716066</v>
+        <v>40.143512663211269</v>
       </c>
       <c r="C196" s="0">
-        <v>0.3063544509794216</v>
+        <v>37.948109283427847</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0">
-        <v>162.02800345814953</v>
+        <v>242.77328350791817</v>
       </c>
       <c r="B197" s="0">
-        <v>-8.3376326517716066</v>
+        <v>41.718549389904091</v>
       </c>
       <c r="C197" s="0">
-        <v>0.3063544509794216</v>
+        <v>40.175547583552564</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0">
-        <v>162.33443705584381</v>
+        <v>243.35412987569779</v>
       </c>
       <c r="B198" s="0">
-        <v>-8.3376326517716066</v>
+        <v>41.718549389904091</v>
       </c>
       <c r="C198" s="0">
-        <v>0.3063544509794216</v>
+        <v>40.175547583552564</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0">
-        <v>162.64087065353809</v>
+        <v>243.93497624347742</v>
       </c>
       <c r="B199" s="0">
-        <v>-8.3376326517716066</v>
+        <v>41.718549389904091</v>
       </c>
       <c r="C199" s="0">
-        <v>0.3063544509794216</v>
+        <v>40.175547583552564</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0">
-        <v>162.94730425123237</v>
+        <v>244.51582261125708</v>
       </c>
       <c r="B200" s="0">
-        <v>-8.3376326517716066</v>
+        <v>41.718549389904091</v>
       </c>
       <c r="C200" s="0">
-        <v>0.3063544509794216</v>
+        <v>40.175547583552564</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0">
-        <v>163.25373784892665</v>
+        <v>245.09666897903668</v>
       </c>
       <c r="B201" s="0">
-        <v>-9.0130049544199622</v>
+        <v>41.718549389904091</v>
       </c>
       <c r="C201" s="0">
-        <v>1.2614751210358726</v>
+        <v>40.175547583552564</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0">
-        <v>163.56017144662093</v>
+        <v>245.67751534681634</v>
       </c>
       <c r="B202" s="0">
-        <v>-9.0130049544199622</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C202" s="0">
-        <v>1.2614751210358726</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0">
-        <v>163.86660504431521</v>
+        <v>246.25836171459596</v>
       </c>
       <c r="B203" s="0">
-        <v>-8.2386447294046725</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C203" s="0">
-        <v>0.16636438865696585</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0">
-        <v>164.17303864200949</v>
+        <v>246.83920808237559</v>
       </c>
       <c r="B204" s="0">
-        <v>-8.2386447294046725</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C204" s="0">
-        <v>0.16636438865696585</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0">
-        <v>164.47947223970374</v>
+        <v>247.42005445015522</v>
       </c>
       <c r="B205" s="0">
-        <v>-8.2386447294046725</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C205" s="0">
-        <v>0.16636438865696585</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0">
-        <v>164.78590583739805</v>
+        <v>248.00090081793485</v>
       </c>
       <c r="B206" s="0">
-        <v>-8.2386447294046725</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C206" s="0">
-        <v>0.16636438865696585</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0">
-        <v>165.0923394350923</v>
+        <v>248.58174718571451</v>
       </c>
       <c r="B207" s="0">
-        <v>-7.8864019135956696</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C207" s="0">
-        <v>0.33178217870861293</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0">
-        <v>165.39877303278658</v>
+        <v>249.16259355349411</v>
       </c>
       <c r="B208" s="0">
-        <v>-7.8864019135956696</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C208" s="0">
-        <v>0.33178217870861293</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0">
-        <v>165.70520663048086</v>
+        <v>249.74343992127376</v>
       </c>
       <c r="B209" s="0">
-        <v>-7.8864019135956696</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C209" s="0">
-        <v>0.33178217870861293</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0">
-        <v>166.01164022817514</v>
+        <v>250.32428628905339</v>
       </c>
       <c r="B210" s="0">
-        <v>-9.253005686633788</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C210" s="0">
-        <v>2.2644517689293617</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0">
-        <v>166.31807382586942</v>
+        <v>250.90513265683302</v>
       </c>
       <c r="B211" s="0">
-        <v>-9.253005686633788</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C211" s="0">
-        <v>2.2644517689293617</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0">
-        <v>166.6245074235637</v>
+        <v>251.48597902461267</v>
       </c>
       <c r="B212" s="0">
-        <v>-9.253005686633788</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C212" s="0">
-        <v>2.2644517689293617</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0">
-        <v>166.93094102125798</v>
+        <v>252.06682539239228</v>
       </c>
       <c r="B213" s="0">
-        <v>-9.253005686633788</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C213" s="0">
-        <v>2.2644517689293617</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0">
-        <v>167.23737461895223</v>
+        <v>252.64767176017193</v>
       </c>
       <c r="B214" s="0">
-        <v>-9.253005686633788</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C214" s="0">
-        <v>2.2644517689293617</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0">
-        <v>167.54380821664654</v>
+        <v>253.22851812795156</v>
       </c>
       <c r="B215" s="0">
-        <v>-9.253005686633788</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C215" s="0">
-        <v>2.2644517689293617</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0">
-        <v>167.85024181434079</v>
+        <v>253.80936449573119</v>
       </c>
       <c r="B216" s="0">
-        <v>-9.253005686633788</v>
+        <v>45.874048031436132</v>
       </c>
       <c r="C216" s="0">
-        <v>2.2644517689293617</v>
+        <v>34.298785046274979</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0">
-        <v>168.1566754120351</v>
+        <v>254.39021086351085</v>
       </c>
       <c r="B217" s="0">
-        <v>-9.253005686633788</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C217" s="0">
-        <v>2.2644517689293617</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0">
-        <v>168.46310900972935</v>
+        <v>254.97105723129044</v>
       </c>
       <c r="B218" s="0">
-        <v>-9.253005686633788</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C218" s="0">
-        <v>2.2644517689293617</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0">
-        <v>168.76954260742363</v>
+        <v>255.5519035990701</v>
       </c>
       <c r="B219" s="0">
-        <v>-9.253005686633788</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C219" s="0">
-        <v>2.2644517689293617</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0">
-        <v>169.07597620511791</v>
+        <v>256.1327499668497</v>
       </c>
       <c r="B220" s="0">
-        <v>-9.9692778370770601</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C220" s="0">
-        <v>3.2774135584363804</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0">
-        <v>169.38240980281219</v>
+        <v>256.71359633462936</v>
       </c>
       <c r="B221" s="0">
-        <v>-9.9692778370770601</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C221" s="0">
-        <v>3.2774135584363804</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0">
-        <v>169.68884340050647</v>
+        <v>257.29444270240902</v>
       </c>
       <c r="B222" s="0">
-        <v>-9.9692778370770601</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C222" s="0">
-        <v>3.2774135584363804</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0">
-        <v>169.99527699820075</v>
+        <v>257.87528907018861</v>
       </c>
       <c r="B223" s="0">
-        <v>-9.9692778370770601</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C223" s="0">
-        <v>3.2774135584363804</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0">
-        <v>170.30171059589503</v>
+        <v>258.45613543796827</v>
       </c>
       <c r="B224" s="0">
-        <v>-9.9692778370770601</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C224" s="0">
-        <v>3.2774135584363804</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0">
-        <v>170.60814419358928</v>
+        <v>259.03698180574793</v>
       </c>
       <c r="B225" s="0">
-        <v>-9.9692778370770601</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C225" s="0">
-        <v>3.2774135584363804</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0">
-        <v>170.91457779128359</v>
+        <v>259.61782817352753</v>
       </c>
       <c r="B226" s="0">
-        <v>-9.9692778370770601</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C226" s="0">
-        <v>3.2774135584363804</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0">
-        <v>171.22101138897784</v>
+        <v>260.19867454130713</v>
       </c>
       <c r="B227" s="0">
-        <v>-9.9692778370770601</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C227" s="0">
-        <v>3.2774135584363804</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0">
-        <v>171.52744498667215</v>
+        <v>260.77952090908678</v>
       </c>
       <c r="B228" s="0">
-        <v>-9.2996023894935807</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C228" s="0">
-        <v>4.224477658797209</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0">
-        <v>171.8338785843664</v>
+        <v>261.36036727686644</v>
       </c>
       <c r="B229" s="0">
-        <v>-9.2996023894935807</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C229" s="0">
-        <v>4.224477658797209</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0">
-        <v>172.14031218206068</v>
+        <v>261.94121364464604</v>
       </c>
       <c r="B230" s="0">
-        <v>-9.2996023894935807</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C230" s="0">
-        <v>4.224477658797209</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0">
-        <v>172.44674577975496</v>
+        <v>262.5220600124257</v>
       </c>
       <c r="B231" s="0">
-        <v>-9.2996023894935807</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C231" s="0">
-        <v>4.224477658797209</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0">
-        <v>172.75317937744922</v>
+        <v>263.10290638020535</v>
       </c>
       <c r="B232" s="0">
-        <v>-9.2352115134785944</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C232" s="0">
-        <v>4.3155401089506871</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0">
-        <v>173.05961297514352</v>
+        <v>263.68375274798496</v>
       </c>
       <c r="B233" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C233" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0">
-        <v>173.3660465728378</v>
+        <v>264.26459911576461</v>
       </c>
       <c r="B234" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C234" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0">
-        <v>173.67248017053208</v>
+        <v>264.84544548354421</v>
       </c>
       <c r="B235" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C235" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0">
-        <v>173.97891376822634</v>
+        <v>265.42629185132387</v>
       </c>
       <c r="B236" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C236" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0">
-        <v>174.28534736592064</v>
+        <v>266.00713821910347</v>
       </c>
       <c r="B237" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C237" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0">
-        <v>174.59178096361489</v>
+        <v>266.58798458688312</v>
       </c>
       <c r="B238" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C238" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0">
-        <v>174.89821456130918</v>
+        <v>267.16883095466278</v>
       </c>
       <c r="B239" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C239" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0">
-        <v>175.20464815900346</v>
+        <v>267.74967732244238</v>
       </c>
       <c r="B240" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C240" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0">
-        <v>175.51108175669773</v>
+        <v>268.33052369022209</v>
       </c>
       <c r="B241" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C241" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0">
-        <v>175.81751535439201</v>
+        <v>268.91137005800169</v>
       </c>
       <c r="B242" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C242" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0">
-        <v>176.1239489520863</v>
+        <v>269.49221642578129</v>
       </c>
       <c r="B243" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C243" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0">
-        <v>176.43038254978058</v>
+        <v>270.07306279356095</v>
       </c>
       <c r="B244" s="0">
-        <v>-10.458206525925194</v>
+        <v>51.924115570228544</v>
       </c>
       <c r="C244" s="0">
-        <v>2.5859639756340549</v>
+        <v>25.742697479641535</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0">
-        <v>176.73681614747483</v>
+        <v>270.65390916134061</v>
       </c>
       <c r="B245" s="0">
-        <v>-10.458206525925194</v>
+        <v>54.962509731425172</v>
       </c>
       <c r="C245" s="0">
-        <v>2.5859639756340549</v>
+        <v>30.039635710241029</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0">
-        <v>177.04324974516913</v>
+        <v>271.23475552912021</v>
       </c>
       <c r="B246" s="0">
-        <v>-10.458206525925194</v>
+        <v>54.962509731425172</v>
       </c>
       <c r="C246" s="0">
-        <v>2.5859639756340549</v>
+        <v>30.039635710241029</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0">
-        <v>177.34968334286339</v>
+        <v>271.81560189689986</v>
       </c>
       <c r="B247" s="0">
-        <v>-10.458206525925194</v>
+        <v>54.962509731425172</v>
       </c>
       <c r="C247" s="0">
-        <v>2.5859639756340549</v>
+        <v>30.039635710241029</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0">
-        <v>177.6561169405577</v>
+        <v>272.39644826467946</v>
       </c>
       <c r="B248" s="0">
-        <v>-10.458206525925194</v>
+        <v>54.962509731425172</v>
       </c>
       <c r="C248" s="0">
-        <v>2.5859639756340549</v>
+        <v>30.039635710241029</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0">
-        <v>177.96255053825195</v>
+        <v>272.97729463245912</v>
       </c>
       <c r="B249" s="0">
-        <v>-10.458206525925194</v>
+        <v>54.962509731425172</v>
       </c>
       <c r="C249" s="0">
-        <v>2.5859639756340549</v>
+        <v>30.039635710241029</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0">
-        <v>178.26898413594623</v>
+        <v>273.55814100023872</v>
       </c>
       <c r="B250" s="0">
-        <v>-10.458206525925194</v>
+        <v>54.962509731425172</v>
       </c>
       <c r="C250" s="0">
-        <v>2.5859639756340549</v>
+        <v>30.039635710241029</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0">
-        <v>178.57541773364051</v>
+        <v>274.13898736801838</v>
       </c>
       <c r="B251" s="0">
-        <v>-12.062371597475314</v>
+        <v>56.552113220783752</v>
       </c>
       <c r="C251" s="0">
-        <v>0.31733197516266776</v>
+        <v>32.287674523687528</v>
       </c>
     </row>
   </sheetData>

--- a/saving_curve_nsga2.xlsx
+++ b/saving_curve_nsga2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="21" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33" uniqueCount="3">
   <si>
     <t>T_deadline_s</t>
   </si>
@@ -88,2748 +88,2744 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>129.50824179088957</v>
+        <v>189.92817092193403</v>
       </c>
       <c r="B2" s="0"/>
       <c r="C2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>130.0890881586692</v>
-      </c>
-      <c r="B3" s="0">
-        <v>0.30654325255556569</v>
-      </c>
-      <c r="C3" s="0">
-        <v>0</v>
-      </c>
+        <v>190.56782276341153</v>
+      </c>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>130.66993452644883</v>
+        <v>191.20747460488903</v>
       </c>
       <c r="B4" s="0">
-        <v>6.4940153317464286</v>
+        <v>4.7505888467250355</v>
       </c>
       <c r="C4" s="0">
-        <v>0.85118293507388954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>131.25078089422848</v>
+        <v>191.84712644636653</v>
       </c>
       <c r="B5" s="0">
-        <v>9.2401139584108734</v>
+        <v>5.7174344902513701</v>
       </c>
       <c r="C5" s="0">
-        <v>0.072208750233284436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>131.83162726200811</v>
+        <v>192.486778287844</v>
       </c>
       <c r="B6" s="0">
-        <v>9.1120508722446907</v>
+        <v>6.2669358462383533</v>
       </c>
       <c r="C6" s="0">
-        <v>0.62236705432419803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>132.41247362978774</v>
+        <v>193.12643012932151</v>
       </c>
       <c r="B7" s="0">
-        <v>10.659984782152558</v>
+        <v>6.4143676390849427</v>
       </c>
       <c r="C7" s="0">
-        <v>0.12126559702265481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>132.99331999756737</v>
+        <v>193.76608197079901</v>
       </c>
       <c r="B8" s="0">
-        <v>10.795219192794811</v>
+        <v>7.1683968168991656</v>
       </c>
       <c r="C8" s="0">
-        <v>0.85675620997698154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>133.574166365347</v>
+        <v>194.40573381227651</v>
       </c>
       <c r="B9" s="0">
-        <v>9.3561577802586324</v>
+        <v>2.8685643512187218</v>
       </c>
       <c r="C9" s="0">
-        <v>3.3188787819684267</v>
+        <v>5.9931937682826648</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>134.15501273312665</v>
+        <v>195.04538565375401</v>
       </c>
       <c r="B10" s="0">
-        <v>6.9019316499164818</v>
+        <v>4.2328673372153132</v>
       </c>
       <c r="C10" s="0">
-        <v>5.960817613835582</v>
+        <v>4.574079296235456</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>134.73585910090628</v>
+        <v>195.68503749523151</v>
       </c>
       <c r="B11" s="0">
-        <v>7.3295890037989482</v>
+        <v>3.9488712692512404</v>
       </c>
       <c r="C11" s="0">
-        <v>8.0651323876131027</v>
+        <v>4.4578407412254668</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>135.31670546868591</v>
+        <v>196.32468933670899</v>
       </c>
       <c r="B12" s="0">
-        <v>1.2085012937915949</v>
+        <v>5.342587635405236</v>
       </c>
       <c r="C12" s="0">
-        <v>1.3268969349796087</v>
+        <v>1.6520696657151772</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>135.89755183646554</v>
+        <v>196.96434117818649</v>
       </c>
       <c r="B13" s="0">
-        <v>2.7877159367733628</v>
+        <v>5.5240528775144213</v>
       </c>
       <c r="C13" s="0">
-        <v>3.7529886261922361</v>
+        <v>3.3988052838978753</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>136.47839820424517</v>
+        <v>197.60399301966399</v>
       </c>
       <c r="B14" s="0">
-        <v>3.8005957949213034</v>
+        <v>5.5505510298041996</v>
       </c>
       <c r="C14" s="0">
-        <v>5.7888916702191313</v>
+        <v>2.8640893017751976</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>137.0592445720248</v>
+        <v>198.24364486114149</v>
       </c>
       <c r="B15" s="0">
-        <v>5.2113467755186633</v>
+        <v>5.9938313820210398</v>
       </c>
       <c r="C15" s="0">
-        <v>7.9439463302272611</v>
+        <v>1.9978378545330515</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>137.64009093980445</v>
+        <v>198.88329670261899</v>
       </c>
       <c r="B16" s="0">
-        <v>1.8620066057103184</v>
+        <v>6.515272609483425</v>
       </c>
       <c r="C16" s="0">
-        <v>4.3208966973964733</v>
+        <v>1.6646147370543825</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>138.22093730758408</v>
+        <v>199.52294854409649</v>
       </c>
       <c r="B17" s="0">
-        <v>2.088238695903426</v>
+        <v>6.4856839911471926</v>
       </c>
       <c r="C17" s="0">
-        <v>3.1513892245842841</v>
+        <v>1.8030820417268314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>138.80178367536371</v>
+        <v>200.162600385574</v>
       </c>
       <c r="B18" s="0">
-        <v>2.3583112024469046</v>
+        <v>6.9052192082464989</v>
       </c>
       <c r="C18" s="0">
-        <v>2.4957539103210826</v>
+        <v>1.8523916423090585</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>139.38263004314334</v>
+        <v>200.80225222705147</v>
       </c>
       <c r="B19" s="0">
-        <v>3.1155555319947199</v>
+        <v>6.5573883456847906</v>
       </c>
       <c r="C19" s="0">
-        <v>4.8831906429798027</v>
+        <v>1.051095787130905</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>139.96347641092296</v>
+        <v>201.44190406852897</v>
       </c>
       <c r="B20" s="0">
-        <v>1.9511555972228996</v>
+        <v>7.2946644514255503</v>
       </c>
       <c r="C20" s="0">
-        <v>5.4802299194742705</v>
+        <v>0.2588933365007256</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>140.54432277870262</v>
+        <v>202.08155591000647</v>
       </c>
       <c r="B21" s="0">
-        <v>3.1170717359970128</v>
+        <v>6.5359570609847353</v>
       </c>
       <c r="C21" s="0">
-        <v>4.4760715616973199</v>
+        <v>0.80127034149640197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>141.12516914648225</v>
+        <v>202.72120775148397</v>
       </c>
       <c r="B22" s="0">
-        <v>4.170479159569064</v>
+        <v>6.2942489511055681</v>
       </c>
       <c r="C22" s="0">
-        <v>6.0797524068961541</v>
+        <v>0.90897958949002344</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>141.70601551426188</v>
+        <v>203.36085959296148</v>
       </c>
       <c r="B23" s="0">
-        <v>3.9501971907633697</v>
+        <v>6.559614495458705</v>
       </c>
       <c r="C23" s="0">
-        <v>6.4467563029343253</v>
+        <v>0.43027331708229266</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>142.28686188204151</v>
+        <v>204.00051143443898</v>
       </c>
       <c r="B24" s="0">
-        <v>4.1504649838351613</v>
+        <v>6.6637706165733874</v>
       </c>
       <c r="C24" s="0">
-        <v>6.469865406789399</v>
+        <v>0.42968540761512591</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>142.86770824982114</v>
+        <v>204.64016327591645</v>
       </c>
       <c r="B25" s="0">
-        <v>4.3302786095995849</v>
+        <v>6.462079683435797</v>
       </c>
       <c r="C25" s="0">
-        <v>7.3505585813053447</v>
+        <v>0.37134918988761423</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>143.44855461760079</v>
+        <v>205.27981511739395</v>
       </c>
       <c r="B26" s="0">
-        <v>4.7649354427910717</v>
+        <v>6.8955185009726048</v>
       </c>
       <c r="C26" s="0">
-        <v>8.9963323162487541</v>
+        <v>0.42902930691498342</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>144.02940098538042</v>
+        <v>205.91946695887145</v>
       </c>
       <c r="B27" s="0">
-        <v>4.7087556317919548</v>
+        <v>6.9266048281260515</v>
       </c>
       <c r="C27" s="0">
-        <v>5.8325094567318683</v>
+        <v>0.068758739578449524</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>144.61024735316005</v>
+        <v>206.55911880034896</v>
       </c>
       <c r="B28" s="0">
-        <v>2.9677497639863555</v>
+        <v>6.0387867688235488</v>
       </c>
       <c r="C28" s="0">
-        <v>4.5252173561851157</v>
+        <v>0.3726484249449053</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>145.19109372093968</v>
+        <v>207.19877064182646</v>
       </c>
       <c r="B29" s="0">
-        <v>2.2001687903632425</v>
+        <v>5.9093563184032334</v>
       </c>
       <c r="C29" s="0">
-        <v>2.9597907419757696</v>
+        <v>0.49378253613636858</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>145.7719400887193</v>
+        <v>207.83842248330396</v>
       </c>
       <c r="B30" s="0">
-        <v>1.8300184041522287</v>
+        <v>6.1004404921142665</v>
       </c>
       <c r="C30" s="0">
-        <v>1.9741441206714252</v>
+        <v>0.59770436751557998</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>146.35278645649896</v>
+        <v>208.47807432478146</v>
       </c>
       <c r="B31" s="0">
-        <v>1.290208848600549</v>
+        <v>6.0389447129323752</v>
       </c>
       <c r="C31" s="0">
-        <v>2.5760406889436513</v>
+        <v>0.063698057905589758</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>146.93363282427859</v>
+        <v>209.11772616625893</v>
       </c>
       <c r="B32" s="0">
-        <v>-0.22979105126502741</v>
+        <v>6.1198564913187514</v>
       </c>
       <c r="C32" s="0">
-        <v>1.9072508436906464</v>
+        <v>0.5381733448596514</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>147.51447919205822</v>
+        <v>209.75737800773644</v>
       </c>
       <c r="B33" s="0">
-        <v>0.50695641918312329</v>
+        <v>6.0194462075391551</v>
       </c>
       <c r="C33" s="0">
-        <v>0.99022449577050031</v>
+        <v>0.27485100657029099</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>148.09532555983785</v>
+        <v>210.39702984921394</v>
       </c>
       <c r="B34" s="0">
-        <v>0.52557940283640769</v>
+        <v>5.7405557478410501</v>
       </c>
       <c r="C34" s="0">
-        <v>1.71807316427339</v>
+        <v>0.089950586380784889</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>148.67617192761747</v>
+        <v>211.03668169069144</v>
       </c>
       <c r="B35" s="0">
-        <v>-0.74619760271361857</v>
+        <v>6.0051203645114697</v>
       </c>
       <c r="C35" s="0">
-        <v>0.33353598327056955</v>
+        <v>0.23508333913435261</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>149.25701829539713</v>
+        <v>211.67633353216894</v>
       </c>
       <c r="B36" s="0">
-        <v>2.1306602128304233</v>
+        <v>5.7707647897760435</v>
       </c>
       <c r="C36" s="0">
-        <v>1.1938169822140696</v>
+        <v>0.31888194697621614</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>149.83786466317676</v>
+        <v>212.31598537364644</v>
       </c>
       <c r="B37" s="0">
-        <v>2.7004394028222189</v>
+        <v>5.9341239701680397</v>
       </c>
       <c r="C37" s="0">
-        <v>3.0953918087073058</v>
+        <v>0.37058646006232621</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>150.41871103095639</v>
+        <v>212.95563721512394</v>
       </c>
       <c r="B38" s="0">
-        <v>-0.11267599661269376</v>
+        <v>6.063811282590283</v>
       </c>
       <c r="C38" s="0">
-        <v>0.78993621646800938</v>
+        <v>0.47216791818426168</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>150.99955739873602</v>
+        <v>213.59528905660142</v>
       </c>
       <c r="B39" s="0">
-        <v>0.014943022361046221</v>
+        <v>5.7113222087371049</v>
       </c>
       <c r="C39" s="0">
-        <v>1.1387254402844924</v>
+        <v>0.54069324621071702</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>151.58040376651565</v>
+        <v>214.23494089807892</v>
       </c>
       <c r="B40" s="0">
-        <v>0.99699114483872164</v>
+        <v>5.9792661988171734</v>
       </c>
       <c r="C40" s="0">
-        <v>0.31468833010481534</v>
+        <v>0.30989797417331177</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>152.1612501342953</v>
+        <v>214.87459273955642</v>
       </c>
       <c r="B41" s="0">
-        <v>2.1288965583063741</v>
+        <v>6.1542137865667668</v>
       </c>
       <c r="C41" s="0">
-        <v>3.1247964843836926</v>
+        <v>0.47369352130343101</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>152.74209650207493</v>
+        <v>215.51424458103392</v>
       </c>
       <c r="B42" s="0">
-        <v>5.3988609889166961</v>
+        <v>5.4060962635035281</v>
       </c>
       <c r="C42" s="0">
-        <v>2.4838011613586386</v>
+        <v>0.34989492418796359</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>153.32294286985456</v>
+        <v>216.15389642251142</v>
       </c>
       <c r="B43" s="0">
-        <v>7.2466371524758433</v>
+        <v>5.4544743180145261</v>
       </c>
       <c r="C43" s="0">
-        <v>3.3161315801606905</v>
+        <v>0.024730580749427675</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>153.90378923763419</v>
+        <v>216.79354826398893</v>
       </c>
       <c r="B44" s="0">
-        <v>7.9490254308194253</v>
+        <v>5.1027931680987688</v>
       </c>
       <c r="C44" s="0">
-        <v>2.4911585706096231</v>
+        <v>0.052790469264290221</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>154.48463560541382</v>
+        <v>217.43320010546643</v>
       </c>
       <c r="B45" s="0">
-        <v>7.9490254308194253</v>
+        <v>5.3782681666260608</v>
       </c>
       <c r="C45" s="0">
-        <v>2.4911585706096231</v>
+        <v>0.079747897048678046</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>155.06548197319347</v>
+        <v>218.0728519469439</v>
       </c>
       <c r="B46" s="0">
-        <v>2.4701328001770619</v>
+        <v>5.3314430321613404</v>
       </c>
       <c r="C46" s="0">
-        <v>10.239482835650058</v>
+        <v>0.013527156828726666</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>155.6463283409731</v>
+        <v>218.7125037884214</v>
       </c>
       <c r="B47" s="0">
-        <v>5.1268274220431085</v>
+        <v>5.0606952288444491</v>
       </c>
       <c r="C47" s="0">
-        <v>13.996616400976681</v>
+        <v>0.44094203374965063</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>156.22717470875273</v>
+        <v>219.3521556298989</v>
       </c>
       <c r="B48" s="0">
-        <v>3.4926529634217589</v>
+        <v>4.9632916373400819</v>
       </c>
       <c r="C48" s="0">
-        <v>16.307688083642706</v>
+        <v>0.20324633863240332</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>156.80802107653236</v>
+        <v>219.99180747137641</v>
       </c>
       <c r="B49" s="0">
-        <v>2.6266422208405746</v>
+        <v>5.1213092382988457</v>
       </c>
       <c r="C49" s="0">
-        <v>17.53241222096181</v>
+        <v>0.21232736782554087</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>157.38886744431198</v>
+        <v>220.63145931285391</v>
       </c>
       <c r="B50" s="0">
-        <v>4.1532368449131294</v>
+        <v>4.7578095805440945</v>
       </c>
       <c r="C50" s="0">
-        <v>19.691343042571074</v>
+        <v>0.17326960927101481</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>157.96971381209164</v>
+        <v>221.27111115433138</v>
       </c>
       <c r="B51" s="0">
-        <v>9.3296842220350449</v>
+        <v>4.9357090354475854</v>
       </c>
       <c r="C51" s="0">
-        <v>13.524504890072205</v>
+        <v>0.21767124076638242</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>158.55056017987127</v>
+        <v>221.91076299580888</v>
       </c>
       <c r="B52" s="0">
-        <v>11.905548431708802</v>
+        <v>4.8408562514221654</v>
       </c>
       <c r="C52" s="0">
-        <v>14.093550920248438</v>
+        <v>0.157276664542878</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>159.1314065476509</v>
+        <v>222.55041483728638</v>
       </c>
       <c r="B53" s="0">
-        <v>11.905548431708802</v>
+        <v>4.9365825699763182</v>
       </c>
       <c r="C53" s="0">
-        <v>14.093550920248438</v>
+        <v>0.12175603276355206</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>159.71225291543053</v>
+        <v>223.19006667876388</v>
       </c>
       <c r="B54" s="0">
-        <v>11.315060753702102</v>
+        <v>4.853966998762739</v>
       </c>
       <c r="C54" s="0">
-        <v>17.540517103034684</v>
+        <v>0.0096124330499446527</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>160.29309928321015</v>
+        <v>223.82971852024139</v>
       </c>
       <c r="B55" s="0">
-        <v>11.315060753702102</v>
+        <v>4.762602436334971</v>
       </c>
       <c r="C55" s="0">
-        <v>17.540517103034684</v>
+        <v>0.086215899775507115</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>160.87394565098978</v>
+        <v>224.46937036171889</v>
       </c>
       <c r="B56" s="0">
-        <v>12.360422776551861</v>
+        <v>4.716684720594702</v>
       </c>
       <c r="C56" s="0">
-        <v>19.018882253338589</v>
+        <v>0.089930583993582169</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>161.45479201876941</v>
+        <v>225.10902220319639</v>
       </c>
       <c r="B57" s="0">
-        <v>12.360422776551861</v>
+        <v>4.7466461010476655</v>
       </c>
       <c r="C57" s="0">
-        <v>19.018882253338589</v>
+        <v>0.14249544200766845</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>162.03563838654907</v>
+        <v>225.74867404467386</v>
       </c>
       <c r="B58" s="0">
-        <v>14.829309688205854</v>
+        <v>4.7888096259824184</v>
       </c>
       <c r="C58" s="0">
-        <v>19.805192988459091</v>
+        <v>0.36348702882833772</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>162.6164847543287</v>
+        <v>226.38832588615136</v>
       </c>
       <c r="B59" s="0">
-        <v>10.833738636447347</v>
+        <v>4.5588911001221053</v>
       </c>
       <c r="C59" s="0">
-        <v>25.455783759281303</v>
+        <v>0.17623974827834338</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>163.19733112210832</v>
+        <v>227.02797772762887</v>
       </c>
       <c r="B60" s="0">
-        <v>10.315111649707184</v>
+        <v>4.3305301323081027</v>
       </c>
       <c r="C60" s="0">
-        <v>27.917368565035762</v>
+        <v>0.030391573123417573</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>163.77817748988795</v>
+        <v>227.66762956910637</v>
       </c>
       <c r="B61" s="0">
-        <v>10.315111649707184</v>
+        <v>4.1368273176107486</v>
       </c>
       <c r="C61" s="0">
-        <v>27.917368565035762</v>
+        <v>0.55183367801427019</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>164.35902385766758</v>
+        <v>228.30728141058387</v>
       </c>
       <c r="B62" s="0">
-        <v>10.315111649707184</v>
+        <v>4.0907378843283864</v>
       </c>
       <c r="C62" s="0">
-        <v>27.917368565035762</v>
+        <v>0.42600844574544039</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>164.93987022544724</v>
+        <v>228.94693325206137</v>
       </c>
       <c r="B63" s="0">
-        <v>10.315111649707184</v>
+        <v>4.2037801670151822</v>
       </c>
       <c r="C63" s="0">
-        <v>27.917368565035762</v>
+        <v>0.44329673148996279</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>165.52071659322687</v>
+        <v>229.58658509353887</v>
       </c>
       <c r="B64" s="0">
-        <v>10.315111649707184</v>
+        <v>3.9174772547524928</v>
       </c>
       <c r="C64" s="0">
-        <v>27.917368565035762</v>
+        <v>0.56313663456631791</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>166.10156296100649</v>
+        <v>230.22623693501635</v>
       </c>
       <c r="B65" s="0">
-        <v>6.5369340770659345</v>
+        <v>3.8492240372109583</v>
       </c>
       <c r="C65" s="0">
-        <v>33.26051852931888</v>
+        <v>0.46661200864347802</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>166.68240932878612</v>
+        <v>230.86588877649385</v>
       </c>
       <c r="B66" s="0">
-        <v>15.027836137464062</v>
+        <v>4.2912522614708575</v>
       </c>
       <c r="C66" s="0">
-        <v>21.252569678722182</v>
+        <v>0.31993034260672293</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>167.26325569656575</v>
+        <v>231.50554061797135</v>
       </c>
       <c r="B67" s="0">
-        <v>13.80832394234211</v>
+        <v>4.1518060657799767</v>
       </c>
       <c r="C67" s="0">
-        <v>22.977220364543033</v>
+        <v>0.12272364143934603</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>167.84410206434541</v>
+        <v>232.14519245944885</v>
       </c>
       <c r="B68" s="0">
-        <v>13.80832394234211</v>
+        <v>4.0546433872699632</v>
       </c>
       <c r="C68" s="0">
-        <v>22.977220364543033</v>
+        <v>0.43620607170539261</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>168.42494843212503</v>
+        <v>232.78484430092635</v>
       </c>
       <c r="B69" s="0">
-        <v>12.52783613746406</v>
+        <v>4.1993585447114423</v>
       </c>
       <c r="C69" s="0">
-        <v>24.788103584654923</v>
+        <v>0.23154793337069576</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>169.00579479990466</v>
+        <v>233.42449614240385</v>
       </c>
       <c r="B70" s="0">
-        <v>12.52783613746406</v>
+        <v>4.2468720534275164</v>
       </c>
       <c r="C70" s="0">
-        <v>24.788103584654923</v>
+        <v>0.68447292696249762</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>169.58664116768432</v>
+        <v>234.06414798388136</v>
       </c>
       <c r="B71" s="0">
-        <v>11.181682291310214</v>
+        <v>4.3254173072398121</v>
       </c>
       <c r="C71" s="0">
-        <v>26.6918526109264</v>
+        <v>0.86004749933132729</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>170.16748753546392</v>
+        <v>234.70379982535883</v>
       </c>
       <c r="B72" s="0">
-        <v>9.7646782427272072</v>
+        <v>4.3899013621797964</v>
       </c>
       <c r="C72" s="0">
-        <v>28.695798954370069</v>
+        <v>0.96896528272744886</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>170.74833390324358</v>
+        <v>235.34345166683633</v>
       </c>
       <c r="B73" s="0">
-        <v>9.7646782427272072</v>
+        <v>4.1089476550092607</v>
       </c>
       <c r="C73" s="0">
-        <v>28.695798954370069</v>
+        <v>0.4677248256077331</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>171.3291802710232</v>
+        <v>235.98310350831383</v>
       </c>
       <c r="B74" s="0">
-        <v>14.921825846764669</v>
+        <v>3.8544225831006918</v>
       </c>
       <c r="C74" s="0">
-        <v>21.40249086958038</v>
+        <v>0.1077720169506476</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>171.91002663880283</v>
+        <v>236.62275534979133</v>
       </c>
       <c r="B75" s="0">
-        <v>14.921825846764669</v>
+        <v>3.9363166425234963</v>
       </c>
       <c r="C75" s="0">
-        <v>21.40249086958038</v>
+        <v>0.47852960245869403</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>172.49087300658246</v>
+        <v>237.26240719126884</v>
       </c>
       <c r="B76" s="0">
-        <v>15.642006193471966</v>
+        <v>4.0939610520827863</v>
       </c>
       <c r="C76" s="0">
-        <v>20.384002055912365</v>
+        <v>0.081770732331202106</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>173.07171937436209</v>
+        <v>237.90205903274631</v>
       </c>
       <c r="B77" s="0">
-        <v>22.598125996875353</v>
+        <v>4.0287853302334025</v>
       </c>
       <c r="C77" s="0">
-        <v>34.212418765997192</v>
+        <v>0.10108090046677241</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>173.65256574214175</v>
+        <v>238.54171087422381</v>
       </c>
       <c r="B78" s="0">
-        <v>22.598125996875353</v>
+        <v>4.1008203325866814</v>
       </c>
       <c r="C78" s="0">
-        <v>34.212418765997192</v>
+        <v>0.02383977251204843</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>174.23341210992138</v>
+        <v>239.18136271570131</v>
       </c>
       <c r="B79" s="0">
-        <v>-3.3091537745960951</v>
+        <v>4.0880241752761819</v>
       </c>
       <c r="C79" s="0">
-        <v>2.4260076510118669</v>
+        <v>0.041936271726815889</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>174.814258477701</v>
+        <v>239.82101455717881</v>
       </c>
       <c r="B80" s="0">
-        <v>-3.3091537745960951</v>
+        <v>4.0580244378509391</v>
       </c>
       <c r="C80" s="0">
-        <v>2.4260076510118669</v>
+        <v>0.036334952157023745</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>175.39510484548063</v>
+        <v>240.46066639865632</v>
       </c>
       <c r="B81" s="0">
-        <v>-4.9004355963512021</v>
+        <v>4.3001210210632355</v>
       </c>
       <c r="C81" s="0">
-        <v>4.6764199848957047</v>
+        <v>0.049454262970887439</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>175.97595121326026</v>
+        <v>241.10031824013382</v>
       </c>
       <c r="B82" s="0">
-        <v>-4.9004355963512021</v>
+        <v>3.9443022794848339</v>
       </c>
       <c r="C82" s="0">
-        <v>4.6764199848957047</v>
+        <v>0.73323154669277446</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>176.55679758103992</v>
+        <v>241.73997008161132</v>
       </c>
       <c r="B83" s="0">
-        <v>-7.1880608285389283</v>
+        <v>3.9178982005378194</v>
       </c>
       <c r="C83" s="0">
-        <v>5.5579392674590418</v>
+        <v>0.14164454382865921</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>177.13764394881955</v>
+        <v>242.37962192308879</v>
       </c>
       <c r="B84" s="0">
-        <v>-7.1880608285389283</v>
+        <v>3.8015634204475912</v>
       </c>
       <c r="C84" s="0">
-        <v>5.5579392674590418</v>
+        <v>0.22734388318739407</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>177.71849031659917</v>
+        <v>243.01927376456632</v>
       </c>
       <c r="B85" s="0">
-        <v>-4.0272709266347491</v>
+        <v>3.8951737653093801</v>
       </c>
       <c r="C85" s="0">
-        <v>3.6227013919074587</v>
+        <v>0.094958863905429986</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>178.2993366843788</v>
+        <v>243.6589256060438</v>
       </c>
       <c r="B86" s="0">
-        <v>-4.0272709266347491</v>
+        <v>3.6989040278656664</v>
       </c>
       <c r="C86" s="0">
-        <v>3.6227013919074587</v>
+        <v>0.26707552408220986</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>178.88018305215843</v>
+        <v>244.2985774475213</v>
       </c>
       <c r="B87" s="0">
-        <v>-7.4948466241892629</v>
+        <v>3.4718251383549452</v>
       </c>
       <c r="C87" s="0">
-        <v>3.7434581049710416</v>
+        <v>0.078005054014039579</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>179.46102941993809</v>
+        <v>244.9382292889988</v>
       </c>
       <c r="B88" s="0">
-        <v>-4.4125872819928294</v>
+        <v>3.5690196644415786</v>
       </c>
       <c r="C88" s="0">
-        <v>8.1024310694564114</v>
+        <v>0.0026974064368529395</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>180.04187578771772</v>
+        <v>245.57788113047627</v>
       </c>
       <c r="B89" s="0">
-        <v>-6.1140235462804888</v>
+        <v>3.4866983405152432</v>
       </c>
       <c r="C89" s="0">
-        <v>5.6962368289873906</v>
+        <v>0.11911733920598554</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>180.62272215549734</v>
+        <v>246.2175329719538</v>
       </c>
       <c r="B90" s="0">
-        <v>-6.1140235462804888</v>
+        <v>3.501547019912199</v>
       </c>
       <c r="C90" s="0">
-        <v>5.6962368289873906</v>
+        <v>0.029445502940107778</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>181.20356852327697</v>
+        <v>246.85718481343127</v>
       </c>
       <c r="B91" s="0">
-        <v>5.366886280745268</v>
+        <v>3.5730173011651392</v>
       </c>
       <c r="C91" s="0">
-        <v>1.8381670498765843</v>
+        <v>0.096347297027662301</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>181.7844148910566</v>
+        <v>247.49683665490878</v>
       </c>
       <c r="B92" s="0">
-        <v>5.366886280745268</v>
+        <v>3.6843479319478489</v>
       </c>
       <c r="C92" s="0">
-        <v>1.8381670498765843</v>
+        <v>0.19537657286161964</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>182.36526125883626</v>
+        <v>248.13648849638628</v>
       </c>
       <c r="B93" s="0">
-        <v>-3.3713690564834748</v>
+        <v>3.3800303203320561</v>
       </c>
       <c r="C93" s="0">
-        <v>0.46999216534533006</v>
+        <v>0.0093251684838792873</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>182.94610762661588</v>
+        <v>248.77614033786378</v>
       </c>
       <c r="B94" s="0">
-        <v>-3.3713690564834748</v>
+        <v>3.7208395125092344</v>
       </c>
       <c r="C94" s="0">
-        <v>0.46999216534533006</v>
+        <v>0.014760085817050905</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>183.52695399439551</v>
+        <v>249.41579217934128</v>
       </c>
       <c r="B95" s="0">
-        <v>-5.3656710507854708</v>
+        <v>3.3768951172587696</v>
       </c>
       <c r="C95" s="0">
-        <v>3.2903610931549236</v>
+        <v>0.079110215505017178</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>184.10780036217514</v>
+        <v>250.05544402081878</v>
       </c>
       <c r="B96" s="0">
-        <v>-5.3656710507854708</v>
+        <v>3.5204312523455705</v>
       </c>
       <c r="C96" s="0">
-        <v>3.2903610931549236</v>
+        <v>0.035195096415449115</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>184.68864672995477</v>
+        <v>250.69509586229629</v>
       </c>
       <c r="B97" s="0">
-        <v>-5.3656710507854708</v>
+        <v>3.6459409640383056</v>
       </c>
       <c r="C97" s="0">
-        <v>3.2903610931549236</v>
+        <v>0.19738188862310208</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>185.26949309773443</v>
+        <v>251.33474770377376</v>
       </c>
       <c r="B98" s="0">
-        <v>-5.6410785810021551</v>
+        <v>3.5083191403989691</v>
       </c>
       <c r="C98" s="0">
-        <v>7.9776898356656218</v>
+        <v>0.11995724139935189</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>185.85033946551405</v>
+        <v>251.97439954525126</v>
       </c>
       <c r="B99" s="0">
-        <v>-0.64355707950399599</v>
+        <v>3.6304134634119523</v>
       </c>
       <c r="C99" s="0">
-        <v>0.91012714999577138</v>
+        <v>0.1996425047653734</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>186.43118583329368</v>
+        <v>252.61405138672876</v>
       </c>
       <c r="B100" s="0">
-        <v>-2.7268904128373253</v>
+        <v>3.9287878591303951</v>
       </c>
       <c r="C100" s="0">
-        <v>2.0361511049481713</v>
+        <v>0.14624273145808411</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>187.01203220107331</v>
+        <v>253.25370322820626</v>
       </c>
       <c r="B101" s="0">
-        <v>-2.7268904128373253</v>
+        <v>3.7395087377551399</v>
       </c>
       <c r="C101" s="0">
-        <v>2.0361511049481713</v>
+        <v>0.39651191784922935</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>187.59287856885294</v>
+        <v>253.89335506968377</v>
       </c>
       <c r="B102" s="0">
-        <v>-2.0198311820662602</v>
+        <v>3.4812613589521453</v>
       </c>
       <c r="C102" s="0">
-        <v>3.0360838585057</v>
+        <v>0.012760562016445962</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0">
-        <v>188.1737249366326</v>
+        <v>254.53300691116124</v>
       </c>
       <c r="B103" s="0">
-        <v>-6.3621353428256437</v>
+        <v>3.6629102943710112</v>
       </c>
       <c r="C103" s="0">
-        <v>3.1048615775893409</v>
+        <v>0.24412982604354905</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0">
-        <v>188.75457130441222</v>
+        <v>255.17265875263877</v>
       </c>
       <c r="B104" s="0">
-        <v>-6.3621353428256437</v>
+        <v>3.7385981105812172</v>
       </c>
       <c r="C104" s="0">
-        <v>3.1048615775893409</v>
+        <v>0.2738711579971666</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0">
-        <v>189.33541767219185</v>
+        <v>255.81231059411624</v>
       </c>
       <c r="B105" s="0">
-        <v>-8.8293536159843882</v>
+        <v>3.7586778001420607</v>
       </c>
       <c r="C105" s="0">
-        <v>6.5940351208251631</v>
+        <v>0.24547418869198026</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0">
-        <v>189.91626403997148</v>
+        <v>256.45196243559377</v>
       </c>
       <c r="B106" s="0">
-        <v>-13.564202100832883</v>
+        <v>3.4137180144537784</v>
       </c>
       <c r="C106" s="0">
-        <v>0.1020518222292796</v>
+        <v>0.13891831952392561</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0">
-        <v>190.49711040775111</v>
+        <v>257.09161427707124</v>
       </c>
       <c r="B107" s="0">
-        <v>-6.3704309755366788</v>
+        <v>3.4315322529179575</v>
       </c>
       <c r="C107" s="0">
-        <v>10.275580512231134</v>
+        <v>0.26722195228262047</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0">
-        <v>191.07795677553077</v>
+        <v>257.73126611854877</v>
       </c>
       <c r="B108" s="0">
-        <v>-8.730061887791674</v>
+        <v>3.5498458080885023</v>
       </c>
       <c r="C108" s="0">
-        <v>6.9385584739253208</v>
+        <v>0.099901317947858004</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0">
-        <v>191.65880314331037</v>
+        <v>258.37091796002625</v>
       </c>
       <c r="B109" s="0">
-        <v>-11.435689593419374</v>
+        <v>3.6751040445428544</v>
       </c>
       <c r="C109" s="0">
-        <v>10.764893869956413</v>
+        <v>0.49807657711830117</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0">
-        <v>192.23964951109002</v>
+        <v>259.01056980150372</v>
       </c>
       <c r="B110" s="0">
-        <v>-11.435689593419374</v>
+        <v>3.7530181740922526</v>
       </c>
       <c r="C110" s="0">
-        <v>10.764893869956413</v>
+        <v>0.24269239169797413</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0">
-        <v>192.82049587886965</v>
+        <v>259.65022164298125</v>
       </c>
       <c r="B111" s="0">
-        <v>-14.031283596899861</v>
+        <v>3.723208382994907</v>
       </c>
       <c r="C111" s="0">
-        <v>7.0941696278200297</v>
+        <v>0.06047033897295697</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0">
-        <v>193.40134224664928</v>
+        <v>260.28987348445872</v>
       </c>
       <c r="B112" s="0">
-        <v>-14.031283596899861</v>
+        <v>3.502521848795205</v>
       </c>
       <c r="C112" s="0">
-        <v>7.0941696278200297</v>
+        <v>0.033302899497426194</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0">
-        <v>193.98218861442894</v>
+        <v>260.9295253259362</v>
       </c>
       <c r="B113" s="0">
-        <v>-14.031283596899861</v>
+        <v>3.2590661297659871</v>
       </c>
       <c r="C113" s="0">
-        <v>7.0941696278200297</v>
+        <v>0.010595890325685361</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0">
-        <v>194.56303498220854</v>
+        <v>261.56917716741373</v>
       </c>
       <c r="B114" s="0">
-        <v>-16.900098021799355</v>
+        <v>3.1471413051271071</v>
       </c>
       <c r="C114" s="0">
-        <v>3.0370533601955945</v>
+        <v>0.055464239935635179</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0">
-        <v>195.14388134998819</v>
+        <v>262.20882900889126</v>
       </c>
       <c r="B115" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.4498086351353425</v>
       </c>
       <c r="C115" s="0">
-        <v>13.46870059402948</v>
+        <v>0.083388811999026979</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0">
-        <v>195.72472771776782</v>
+        <v>262.84848085036873</v>
       </c>
       <c r="B116" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.4643135972864529</v>
       </c>
       <c r="C116" s="0">
-        <v>13.46870059402948</v>
+        <v>0.2252901343968105</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0">
-        <v>196.30557408554745</v>
+        <v>263.4881326918462</v>
       </c>
       <c r="B117" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.6552759372032364</v>
       </c>
       <c r="C117" s="0">
-        <v>13.46870059402948</v>
+        <v>0.34825846590729265</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0">
-        <v>196.8864204533271</v>
+        <v>264.12778453332373</v>
       </c>
       <c r="B118" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.3430808033614356</v>
       </c>
       <c r="C118" s="0">
-        <v>13.46870059402948</v>
+        <v>0.12895260345629872</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0">
-        <v>197.46726682110671</v>
+        <v>264.76743637480121</v>
       </c>
       <c r="B119" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.6017589080939665</v>
       </c>
       <c r="C119" s="0">
-        <v>13.46870059402948</v>
+        <v>0.088909133455379513</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0">
-        <v>198.04811318888636</v>
+        <v>265.40708821627868</v>
       </c>
       <c r="B120" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.5634741900608775</v>
       </c>
       <c r="C120" s="0">
-        <v>13.46870059402948</v>
+        <v>0.14202603876904088</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0">
-        <v>198.62895955666599</v>
+        <v>266.04674005775621</v>
       </c>
       <c r="B121" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.5201814392798343</v>
       </c>
       <c r="C121" s="0">
-        <v>13.46870059402948</v>
+        <v>0.0071885554304085813</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0">
-        <v>199.20980592444562</v>
+        <v>266.68639189923368</v>
       </c>
       <c r="B122" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.4944856525127852</v>
       </c>
       <c r="C122" s="0">
-        <v>13.46870059402948</v>
+        <v>0.16694640188811805</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0">
-        <v>199.79065229222528</v>
+        <v>267.32604374071121</v>
       </c>
       <c r="B123" s="0">
-        <v>-9.5238095238095255</v>
+        <v>3.5226569773068714</v>
       </c>
       <c r="C123" s="0">
-        <v>13.46870059402948</v>
+        <v>0.12710613229430384</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0">
-        <v>200.37149866000487</v>
+        <v>267.96569558218869</v>
       </c>
       <c r="B124" s="0">
-        <v>8.1310481698034405</v>
+        <v>3.2053125259429729</v>
       </c>
       <c r="C124" s="0">
-        <v>11.499038598044958</v>
+        <v>0.040853810242859369</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0">
-        <v>200.95234502778453</v>
+        <v>268.60534742366622</v>
       </c>
       <c r="B125" s="0">
-        <v>8.1310481698034405</v>
+        <v>3.3848461101134264</v>
       </c>
       <c r="C125" s="0">
-        <v>11.499038598044958</v>
+        <v>0.2977282060075952</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0">
-        <v>201.53319139556416</v>
+        <v>269.24499926514369</v>
       </c>
       <c r="B126" s="0">
-        <v>8.1310481698034405</v>
+        <v>3.4538953045417804</v>
       </c>
       <c r="C126" s="0">
-        <v>11.499038598044958</v>
+        <v>0.18028018563079254</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0">
-        <v>202.11403776334379</v>
+        <v>269.88465110662116</v>
       </c>
       <c r="B127" s="0">
-        <v>-5.2022851635298846</v>
+        <v>3.5944666533913647</v>
       </c>
       <c r="C127" s="0">
-        <v>30.355219429686212</v>
+        <v>0.37907809365495426</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0">
-        <v>202.69488413112342</v>
+        <v>270.52430294809869</v>
       </c>
       <c r="B128" s="0">
-        <v>-5.2022851635298846</v>
+        <v>3.4165866891479864</v>
       </c>
       <c r="C128" s="0">
-        <v>30.355219429686212</v>
+        <v>0.63063835156238146</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0">
-        <v>203.27573049890304</v>
+        <v>271.16395478957617</v>
       </c>
       <c r="B129" s="0">
-        <v>-5.2022851635298846</v>
+        <v>3.406725302236751</v>
       </c>
       <c r="C129" s="0">
-        <v>30.355219429686212</v>
+        <v>0.3187815589212295</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0">
-        <v>203.8565768666827</v>
+        <v>271.8036066310537</v>
       </c>
       <c r="B130" s="0">
-        <v>-5.2022851635298846</v>
+        <v>3.4079711388937506</v>
       </c>
       <c r="C130" s="0">
-        <v>30.355219429686212</v>
+        <v>0.17335499273611055</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0">
-        <v>204.4374232344623</v>
+        <v>272.44325847253117</v>
       </c>
       <c r="B131" s="0">
-        <v>-9.7260946873394243</v>
+        <v>3.3541640240656889</v>
       </c>
       <c r="C131" s="0">
-        <v>36.752852211850232</v>
+        <v>0.030449442912174964</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0">
-        <v>205.01826960224196</v>
+        <v>273.0829103140087</v>
       </c>
       <c r="B132" s="0">
-        <v>-9.7260946873394243</v>
+        <v>3.3665320286652651</v>
       </c>
       <c r="C132" s="0">
-        <v>36.752852211850232</v>
+        <v>0.034749720802251256</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0">
-        <v>205.59911597002159</v>
+        <v>273.72256215548617</v>
       </c>
       <c r="B133" s="0">
-        <v>-9.7260946873394243</v>
+        <v>3.4118429855941233</v>
       </c>
       <c r="C133" s="0">
-        <v>36.752852211850232</v>
+        <v>0.036025033929238788</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0">
-        <v>206.17996233780122</v>
+        <v>274.36221399696365</v>
       </c>
       <c r="B134" s="0">
-        <v>12.958270992919239</v>
+        <v>3.5369458045905002</v>
       </c>
       <c r="C134" s="0">
-        <v>28.512798854731369</v>
+        <v>0.016729810456528816</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0">
-        <v>206.76080870558087</v>
+        <v>275.00186583844118</v>
       </c>
       <c r="B135" s="0">
-        <v>12.958270992919239</v>
+        <v>3.489695002360877</v>
       </c>
       <c r="C135" s="0">
-        <v>28.512798854731369</v>
+        <v>0.27858302790771655</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0">
-        <v>207.3416550733605</v>
+        <v>275.64151767991865</v>
       </c>
       <c r="B136" s="0">
-        <v>12.958270992919239</v>
+        <v>3.6519023675940536</v>
       </c>
       <c r="C136" s="0">
-        <v>28.512798854731369</v>
+        <v>0.17219032909347906</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0">
-        <v>207.92250144114013</v>
+        <v>276.28116952139618</v>
       </c>
       <c r="B137" s="0">
-        <v>12.958270992919239</v>
+        <v>3.2783432696393247</v>
       </c>
       <c r="C137" s="0">
-        <v>28.512798854731369</v>
+        <v>0.07015499803512544</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0">
-        <v>208.50334780891978</v>
+        <v>276.92082136287365</v>
       </c>
       <c r="B138" s="0">
-        <v>12.958270992919239</v>
+        <v>3.453159546141424</v>
       </c>
       <c r="C138" s="0">
-        <v>28.512798854731369</v>
+        <v>0.05298990197841142</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0">
-        <v>209.08419417669939</v>
+        <v>277.56047320435118</v>
       </c>
       <c r="B139" s="0">
-        <v>12.958270992919239</v>
+        <v>3.4199839799060943</v>
       </c>
       <c r="C139" s="0">
-        <v>28.512798854731369</v>
+        <v>0.13316727966090683</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0">
-        <v>209.66504054447904</v>
+        <v>278.20012504582866</v>
       </c>
       <c r="B140" s="0">
-        <v>12.095727593666766</v>
+        <v>3.6140039029900919</v>
       </c>
       <c r="C140" s="0">
-        <v>29.73261942808961</v>
+        <v>0.14586424406752976</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0">
-        <v>210.24588691225867</v>
+        <v>278.83977688730613</v>
       </c>
       <c r="B141" s="0">
-        <v>12.095727593666766</v>
+        <v>3.4067494839454122</v>
       </c>
       <c r="C141" s="0">
-        <v>29.73261942808961</v>
+        <v>0.2919825334841481</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0">
-        <v>210.8267332800383</v>
+        <v>279.47942872878366</v>
       </c>
       <c r="B142" s="0">
-        <v>12.095727593666766</v>
+        <v>3.6950631191431969</v>
       </c>
       <c r="C142" s="0">
-        <v>29.73261942808961</v>
+        <v>0.34750752267799062</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0">
-        <v>211.40757964781795</v>
+        <v>280.11908057026113</v>
       </c>
       <c r="B143" s="0">
-        <v>12.095727593666766</v>
+        <v>3.4865298426145439</v>
       </c>
       <c r="C143" s="0">
-        <v>29.73261942808961</v>
+        <v>0.13815546310670185</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0">
-        <v>211.98842601559755</v>
+        <v>280.75873241173861</v>
       </c>
       <c r="B144" s="0">
-        <v>7.1444362651952034</v>
+        <v>3.3641682658960979</v>
       </c>
       <c r="C144" s="0">
-        <v>36.734802776074389</v>
+        <v>0.034889938201880522</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0">
-        <v>212.56927238337721</v>
+        <v>281.39838425321614</v>
       </c>
       <c r="B145" s="0">
-        <v>9.2863030089165886</v>
+        <v>3.2886474761780145</v>
       </c>
       <c r="C145" s="0">
-        <v>35.952401827880557</v>
+        <v>0.093985132515337397</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0">
-        <v>213.15011875115684</v>
+        <v>282.03803609469367</v>
       </c>
       <c r="B146" s="0">
-        <v>9.2863030089165886</v>
+        <v>3.3391495797046051</v>
       </c>
       <c r="C146" s="0">
-        <v>35.952401827880557</v>
+        <v>0.022564372779663371</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0">
-        <v>213.73096511893647</v>
+        <v>282.67768793617114</v>
       </c>
       <c r="B147" s="0">
-        <v>9.2863030089165886</v>
+        <v>3.1993916375196503</v>
       </c>
       <c r="C147" s="0">
-        <v>35.952401827880557</v>
+        <v>0.17508320450765438</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0">
-        <v>214.3118114867161</v>
+        <v>283.31733977764861</v>
       </c>
       <c r="B148" s="0">
-        <v>10.814982265305092</v>
+        <v>3.5056278113972246</v>
       </c>
       <c r="C148" s="0">
-        <v>38.114280764783601</v>
+        <v>0.18308538658101606</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0">
-        <v>214.89265785449572</v>
+        <v>283.95699161912614</v>
       </c>
       <c r="B149" s="0">
-        <v>22.90053908951975</v>
+        <v>3.3035220274418204</v>
       </c>
       <c r="C149" s="0">
-        <v>34.073570331404277</v>
+        <v>0.095935651382382081</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0">
-        <v>215.47350422227538</v>
+        <v>284.59664346060362</v>
       </c>
       <c r="B150" s="0">
-        <v>17.840883411967109</v>
+        <v>3.3744608634646598</v>
       </c>
       <c r="C150" s="0">
-        <v>41.229004011537249</v>
+        <v>0.13999285027277664</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0">
-        <v>216.05435059005498</v>
+        <v>285.23629530208115</v>
       </c>
       <c r="B151" s="0">
-        <v>17.840883411967109</v>
+        <v>3.3358254837072479</v>
       </c>
       <c r="C151" s="0">
-        <v>41.229004011537249</v>
+        <v>0.099177005199705251</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0">
-        <v>216.63519695783464</v>
+        <v>285.87594714355862</v>
       </c>
       <c r="B152" s="0">
-        <v>17.840883411967109</v>
+        <v>3.3657640998098213</v>
       </c>
       <c r="C152" s="0">
-        <v>41.229004011537249</v>
+        <v>0.19327801641997383</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0">
-        <v>217.21604332561427</v>
+        <v>286.51559898503615</v>
       </c>
       <c r="B153" s="0">
-        <v>17.840883411967102</v>
+        <v>3.2625449495139369</v>
       </c>
       <c r="C153" s="0">
-        <v>41.229004011537256</v>
+        <v>0.024241722122067336</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0">
-        <v>217.79688969339389</v>
+        <v>287.15525082651362</v>
       </c>
       <c r="B154" s="0">
-        <v>17.840883411967102</v>
+        <v>3.1086160264275398</v>
       </c>
       <c r="C154" s="0">
-        <v>41.229004011537256</v>
+        <v>0.090442865508496326</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0">
-        <v>218.37773606117355</v>
+        <v>287.7949026679911</v>
       </c>
       <c r="B155" s="0">
-        <v>11.656859806069424</v>
+        <v>3.2046116642872153</v>
       </c>
       <c r="C155" s="0">
-        <v>49.974534065033133</v>
+        <v>0.22620119849830533</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0">
-        <v>218.95858242895315</v>
+        <v>288.43455450946863</v>
       </c>
       <c r="B156" s="0">
-        <v>11.656859806069424</v>
+        <v>3.2912624862545497</v>
       </c>
       <c r="C156" s="0">
-        <v>49.974534065033133</v>
+        <v>0.34874396611528635</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0">
-        <v>219.53942879673281</v>
+        <v>289.0742063509461</v>
       </c>
       <c r="B157" s="0">
-        <v>11.656859806069424</v>
+        <v>3.3683956282260672</v>
       </c>
       <c r="C157" s="0">
-        <v>49.974534065033133</v>
+        <v>0.17070610609678052</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0">
-        <v>220.12027516451244</v>
+        <v>289.71385819242357</v>
       </c>
       <c r="B158" s="0">
-        <v>11.656859806069424</v>
+        <v>3.466248206424142</v>
       </c>
       <c r="C158" s="0">
-        <v>49.974534065033133</v>
+        <v>0.16408429642380093</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0">
-        <v>220.70112153229206</v>
+        <v>290.3535100339011</v>
       </c>
       <c r="B159" s="0">
-        <v>11.656859806069415</v>
+        <v>3.321211189036462</v>
       </c>
       <c r="C159" s="0">
-        <v>49.97453406503314</v>
+        <v>0.13427755489651749</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0">
-        <v>221.28196790007172</v>
+        <v>290.99316187537863</v>
       </c>
       <c r="B160" s="0">
-        <v>11.656859806069415</v>
+        <v>3.3180260926455096</v>
       </c>
       <c r="C160" s="0">
-        <v>49.97453406503314</v>
+        <v>0.38353818990207184</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0">
-        <v>221.86281426785132</v>
+        <v>291.63281371685611</v>
       </c>
       <c r="B161" s="0">
-        <v>11.656859806069415</v>
+        <v>3.1666790876492237</v>
       </c>
       <c r="C161" s="0">
-        <v>49.97453406503314</v>
+        <v>0.38273728588230982</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0">
-        <v>222.44366063563098</v>
+        <v>292.27246555833358</v>
       </c>
       <c r="B162" s="0">
-        <v>11.656859806069415</v>
+        <v>3.3093062324974527</v>
       </c>
       <c r="C162" s="0">
-        <v>49.97453406503314</v>
+        <v>0.11167541911781401</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0">
-        <v>223.0245070034106</v>
+        <v>292.91211739981111</v>
       </c>
       <c r="B163" s="0">
-        <v>11.656859806069415</v>
+        <v>3.0894902380476186</v>
       </c>
       <c r="C163" s="0">
-        <v>49.97453406503314</v>
+        <v>0.1551728400977351</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0">
-        <v>223.60535337119023</v>
+        <v>293.55176924128858</v>
       </c>
       <c r="B164" s="0">
-        <v>3.9268302986973254</v>
+        <v>3.2085665308256917</v>
       </c>
       <c r="C164" s="0">
-        <v>60.906446631902966</v>
+        <v>0.013226468106125594</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0">
-        <v>224.18619973896989</v>
+        <v>294.19142108276606</v>
       </c>
       <c r="B165" s="0">
-        <v>3.9268302986973254</v>
+        <v>3.1703242374440097</v>
       </c>
       <c r="C165" s="0">
-        <v>60.906446631902966</v>
+        <v>0.04085630185049987</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0">
-        <v>224.76704610674952</v>
+        <v>294.83107292424359</v>
       </c>
       <c r="B166" s="0">
-        <v>3.9268302986973254</v>
+        <v>3.1272109504663179</v>
       </c>
       <c r="C166" s="0">
-        <v>60.906446631902966</v>
+        <v>0.084481565447194235</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0">
-        <v>225.34789247452915</v>
+        <v>295.47072476572106</v>
       </c>
       <c r="B167" s="0">
-        <v>3.9268302986973254</v>
+        <v>2.9774539242580711</v>
       </c>
       <c r="C167" s="0">
-        <v>60.906446631902966</v>
+        <v>0.14293398000923069</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0">
-        <v>225.92873884230877</v>
+        <v>296.11037660719859</v>
       </c>
       <c r="B168" s="0">
-        <v>3.9268302986973254</v>
+        <v>2.9774539242580711</v>
       </c>
       <c r="C168" s="0">
-        <v>60.906446631902966</v>
+        <v>0.14293398000923069</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0">
-        <v>226.5095852100884</v>
+        <v>296.75002844867606</v>
       </c>
       <c r="B169" s="0">
-        <v>3.9268302986973254</v>
+        <v>3.0135944403413646</v>
       </c>
       <c r="C169" s="0">
-        <v>60.906446631902966</v>
+        <v>0.57977235576629116</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0">
-        <v>227.09043157786806</v>
+        <v>297.38968029015359</v>
       </c>
       <c r="B170" s="0">
-        <v>3.9268302986973254</v>
+        <v>2.8334601457294566</v>
       </c>
       <c r="C170" s="0">
-        <v>60.906446631902966</v>
+        <v>0.47911320103328586</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0">
-        <v>227.67127794564766</v>
+        <v>298.02933213163107</v>
       </c>
       <c r="B171" s="0">
-        <v>16.070853742975693</v>
+        <v>2.7007883005548763</v>
       </c>
       <c r="C171" s="0">
-        <v>43.732203975227669</v>
+        <v>0.65398303984895445</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0">
-        <v>228.25212431342732</v>
+        <v>298.6689839731086</v>
       </c>
       <c r="B172" s="0">
-        <v>16.070853742975693</v>
+        <v>2.7513677072182965</v>
       </c>
       <c r="C172" s="0">
-        <v>43.732203975227669</v>
+        <v>0.72551312272914736</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0">
-        <v>228.83297068120694</v>
+        <v>299.30863581458607</v>
       </c>
       <c r="B173" s="0">
-        <v>16.070853742975693</v>
+        <v>2.5580733941351315</v>
       </c>
       <c r="C173" s="0">
-        <v>43.732203975227669</v>
+        <v>0.81928211377453197</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0">
-        <v>229.41381704898657</v>
+        <v>299.9482876560636</v>
       </c>
       <c r="B174" s="0">
-        <v>20.710786903514283</v>
+        <v>2.4664877006894224</v>
       </c>
       <c r="C174" s="0">
-        <v>50.294060379366002</v>
+        <v>0.68976038398426576</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0">
-        <v>229.99466341676623</v>
+        <v>300.58793949754107</v>
       </c>
       <c r="B175" s="0">
-        <v>20.710786903514283</v>
+        <v>2.5429881032417763</v>
       </c>
       <c r="C175" s="0">
-        <v>50.294060379366002</v>
+        <v>0.96129587103326131</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0">
-        <v>230.57550978454583</v>
+        <v>301.22759133901855</v>
       </c>
       <c r="B176" s="0">
-        <v>20.710786903514283</v>
+        <v>2.4715872303043645</v>
       </c>
       <c r="C176" s="0">
-        <v>50.294060379366002</v>
+        <v>0.86031978815989541</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0">
-        <v>231.15635615232549</v>
+        <v>301.86724318049608</v>
       </c>
       <c r="B177" s="0">
-        <v>29.837907985717607</v>
+        <v>3.3212229197025742</v>
       </c>
       <c r="C177" s="0">
-        <v>45.988421102026727</v>
+        <v>0.074995867247676054</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0">
-        <v>231.73720252010512</v>
+        <v>302.50689502197355</v>
       </c>
       <c r="B178" s="0">
-        <v>29.837907985717607</v>
+        <v>3.1646059102882731</v>
       </c>
       <c r="C178" s="0">
-        <v>45.988421102026727</v>
+        <v>0.14649403156434362</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0">
-        <v>232.31804888788474</v>
+        <v>303.14654686345102</v>
       </c>
       <c r="B179" s="0">
-        <v>29.837907985717607</v>
+        <v>2.9967378176092181</v>
       </c>
       <c r="C179" s="0">
-        <v>45.988421102026727</v>
+        <v>0.007744038630805191</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0">
-        <v>232.8988952556644</v>
+        <v>303.78619870492855</v>
       </c>
       <c r="B180" s="0">
-        <v>29.837907985717607</v>
+        <v>3.0616151169620158</v>
       </c>
       <c r="C180" s="0">
-        <v>45.988421102026727</v>
+        <v>0.08400631800406122</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0">
-        <v>233.479741623444</v>
+        <v>304.42585054640608</v>
       </c>
       <c r="B181" s="0">
-        <v>29.837907985717607</v>
+        <v>3.0785697010637674</v>
       </c>
       <c r="C181" s="0">
-        <v>45.988421102026727</v>
+        <v>0.037520428913845494</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0">
-        <v>234.06058799122366</v>
+        <v>305.06550238788356</v>
       </c>
       <c r="B182" s="0">
-        <v>29.837907985717607</v>
+        <v>3.2191777482105217</v>
       </c>
       <c r="C182" s="0">
-        <v>45.988421102026727</v>
+        <v>0.086237862615975727</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0">
-        <v>234.64143435900329</v>
+        <v>305.70515422936103</v>
       </c>
       <c r="B183" s="0">
-        <v>31.409961930094021</v>
+        <v>3.1246125399120421</v>
       </c>
       <c r="C183" s="0">
-        <v>48.211641110945976</v>
+        <v>0.047497537488371169</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0">
-        <v>235.22228072678291</v>
+        <v>306.34480607083856</v>
       </c>
       <c r="B184" s="0">
-        <v>31.409961930094021</v>
+        <v>3.1789994360662517</v>
       </c>
       <c r="C184" s="0">
-        <v>48.211641110945976</v>
+        <v>0.1113850648151072</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0">
-        <v>235.80312709456254</v>
+        <v>306.98445791231603</v>
       </c>
       <c r="B185" s="0">
-        <v>31.409961930094021</v>
+        <v>3.2739962126880879</v>
       </c>
       <c r="C185" s="0">
-        <v>48.211641110945976</v>
+        <v>0.24573079469543602</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0">
-        <v>236.38397346234217</v>
+        <v>307.62410975379351</v>
       </c>
       <c r="B186" s="0">
-        <v>31.409961930094021</v>
+        <v>3.2739962126880879</v>
       </c>
       <c r="C186" s="0">
-        <v>48.211641110945976</v>
+        <v>0.24573079469543602</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0">
-        <v>236.96481983012183</v>
+        <v>308.26376159527104</v>
       </c>
       <c r="B187" s="0">
-        <v>31.409961930094021</v>
+        <v>3.2739962126880879</v>
       </c>
       <c r="C187" s="0">
-        <v>48.211641110945976</v>
+        <v>0.24573079469543602</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0">
-        <v>237.54566619790143</v>
+        <v>308.90341343674851</v>
       </c>
       <c r="B188" s="0">
-        <v>37.47182851184057</v>
+        <v>3.1520589094584364</v>
       </c>
       <c r="C188" s="0">
-        <v>39.638867177743769</v>
+        <v>0.41817618268201018</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0">
-        <v>238.12651256568108</v>
+        <v>309.54306527822604</v>
       </c>
       <c r="B189" s="0">
-        <v>37.47182851184057</v>
+        <v>3.1520589094584364</v>
       </c>
       <c r="C189" s="0">
-        <v>39.638867177743769</v>
+        <v>0.41817618268201018</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0">
-        <v>238.70735893346071</v>
+        <v>310.18271711970351</v>
       </c>
       <c r="B190" s="0">
-        <v>37.47182851184057</v>
+        <v>3.1520589094584364</v>
       </c>
       <c r="C190" s="0">
-        <v>39.638867177743769</v>
+        <v>0.41817618268201018</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0">
-        <v>239.28820530124034</v>
+        <v>310.82236896118104</v>
       </c>
       <c r="B191" s="0">
-        <v>37.47182851184057</v>
+        <v>2.6829316754177008</v>
       </c>
       <c r="C191" s="0">
-        <v>39.638867177743769</v>
+        <v>0.24526991417697511</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0">
-        <v>239.86905166902</v>
+        <v>311.46202080265851</v>
       </c>
       <c r="B192" s="0">
-        <v>37.47182851184057</v>
+        <v>2.6829316754177008</v>
       </c>
       <c r="C192" s="0">
-        <v>39.638867177743769</v>
+        <v>0.24526991417697511</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0">
-        <v>240.4498980367996</v>
+        <v>312.10167264413599</v>
       </c>
       <c r="B193" s="0">
-        <v>40.143512663211269</v>
+        <v>2.7447339599927254</v>
       </c>
       <c r="C193" s="0">
-        <v>37.948109283427847</v>
+        <v>0.33267154320861608</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0">
-        <v>241.03074440457925</v>
+        <v>312.74132448561352</v>
       </c>
       <c r="B194" s="0">
-        <v>40.143512663211269</v>
+        <v>2.4747544802962471</v>
       </c>
       <c r="C194" s="0">
-        <v>37.948109283427847</v>
+        <v>0.71448018495780719</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0">
-        <v>241.61159077235891</v>
+        <v>313.38097632709099</v>
       </c>
       <c r="B195" s="0">
-        <v>40.143512663211269</v>
+        <v>2.9961188235856904</v>
       </c>
       <c r="C195" s="0">
-        <v>37.948109283427847</v>
+        <v>0.12706046750357736</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0">
-        <v>242.19243714013851</v>
+        <v>314.02062816856852</v>
       </c>
       <c r="B196" s="0">
-        <v>40.143512663211269</v>
+        <v>3.0394541753231814</v>
       </c>
       <c r="C196" s="0">
-        <v>37.948109283427847</v>
+        <v>0.065775025346209382</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0">
-        <v>242.77328350791817</v>
+        <v>314.660280010046</v>
       </c>
       <c r="B197" s="0">
-        <v>41.718549389904091</v>
+        <v>3.0394541753231814</v>
       </c>
       <c r="C197" s="0">
-        <v>40.175547583552564</v>
+        <v>0.065775025346209382</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0">
-        <v>243.35412987569779</v>
+        <v>315.29993185152352</v>
       </c>
       <c r="B198" s="0">
-        <v>41.718549389904091</v>
+        <v>2.9982509081158075</v>
       </c>
       <c r="C198" s="0">
-        <v>40.175547583552564</v>
+        <v>0.42882876789240621</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0">
-        <v>243.93497624347742</v>
+        <v>315.939583693001</v>
       </c>
       <c r="B199" s="0">
-        <v>41.718549389904091</v>
+        <v>2.7365646897782128</v>
       </c>
       <c r="C199" s="0">
-        <v>40.175547583552564</v>
+        <v>0.058748568833253079</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0">
-        <v>244.51582261125708</v>
+        <v>316.57923553447847</v>
       </c>
       <c r="B200" s="0">
-        <v>41.718549389904091</v>
+        <v>2.781772166068075</v>
       </c>
       <c r="C200" s="0">
-        <v>40.175547583552564</v>
+        <v>0.00090087928439754419</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0">
-        <v>245.09666897903668</v>
+        <v>317.218887375956</v>
       </c>
       <c r="B201" s="0">
-        <v>41.718549389904091</v>
+        <v>2.8809426277102084</v>
       </c>
       <c r="C201" s="0">
-        <v>40.175547583552564</v>
+        <v>0.13934733255670861</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0">
-        <v>245.67751534681634</v>
+        <v>317.85853921743347</v>
       </c>
       <c r="B202" s="0">
-        <v>45.874048031436132</v>
+        <v>3.0303673688310093</v>
       </c>
       <c r="C202" s="0">
-        <v>34.298785046274979</v>
+        <v>0.03642603658362472</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0">
-        <v>246.25836171459596</v>
+        <v>318.498191058911</v>
       </c>
       <c r="B203" s="0">
-        <v>45.874048031436132</v>
+        <v>3.1095082902292779</v>
       </c>
       <c r="C203" s="0">
-        <v>34.298785046274979</v>
+        <v>0.075496127796509771</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0">
-        <v>246.83920808237559</v>
+        <v>319.13784290038848</v>
       </c>
       <c r="B204" s="0">
-        <v>45.874048031436132</v>
+        <v>2.8181455038857761</v>
       </c>
       <c r="C204" s="0">
-        <v>34.298785046274979</v>
+        <v>0.059108599075696794</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0">
-        <v>247.42005445015522</v>
+        <v>319.77749474186601</v>
       </c>
       <c r="B205" s="0">
-        <v>45.874048031436132</v>
+        <v>2.756527297958578</v>
       </c>
       <c r="C205" s="0">
-        <v>34.298785046274979</v>
+        <v>0.028032703435645037</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0">
-        <v>248.00090081793485</v>
+        <v>320.41714658334348</v>
       </c>
       <c r="B206" s="0">
-        <v>45.874048031436132</v>
+        <v>2.9314546757795896</v>
       </c>
       <c r="C206" s="0">
-        <v>34.298785046274979</v>
+        <v>0.0018506735280377493</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0">
-        <v>248.58174718571451</v>
+        <v>321.05679842482095</v>
       </c>
       <c r="B207" s="0">
-        <v>45.874048031436132</v>
+        <v>2.8249699410692761</v>
       </c>
       <c r="C207" s="0">
-        <v>34.298785046274979</v>
+        <v>0.15244282954106384</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0">
-        <v>249.16259355349411</v>
+        <v>321.69645026629849</v>
       </c>
       <c r="B208" s="0">
-        <v>45.874048031436132</v>
+        <v>2.9228407144887942</v>
       </c>
       <c r="C208" s="0">
-        <v>34.298785046274979</v>
+        <v>0.014032654411237758</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0">
-        <v>249.74343992127376</v>
+        <v>322.33610210777596</v>
       </c>
       <c r="B209" s="0">
-        <v>45.874048031436132</v>
+        <v>2.7466302166996948</v>
       </c>
       <c r="C209" s="0">
-        <v>34.298785046274979</v>
+        <v>0.12925969963136058</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0">
-        <v>250.32428628905339</v>
+        <v>322.97575394925349</v>
       </c>
       <c r="B210" s="0">
-        <v>45.874048031436132</v>
+        <v>2.7981509539817586</v>
       </c>
       <c r="C210" s="0">
-        <v>34.298785046274979</v>
+        <v>0.28717486273314935</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0">
-        <v>250.90513265683302</v>
+        <v>323.61540579073096</v>
       </c>
       <c r="B211" s="0">
-        <v>45.874048031436132</v>
+        <v>2.8183309474022291</v>
       </c>
       <c r="C211" s="0">
-        <v>34.298785046274979</v>
+        <v>0.060675906817093298</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0">
-        <v>251.48597902461267</v>
+        <v>324.25505763220849</v>
       </c>
       <c r="B212" s="0">
-        <v>45.874048031436132</v>
+        <v>2.6032054802119333</v>
       </c>
       <c r="C212" s="0">
-        <v>34.298785046274979</v>
+        <v>0.19505120922281746</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0">
-        <v>252.06682539239228</v>
+        <v>324.89470947368596</v>
       </c>
       <c r="B213" s="0">
-        <v>45.874048031436132</v>
+        <v>2.664203693285498</v>
       </c>
       <c r="C213" s="0">
-        <v>34.298785046274979</v>
+        <v>0.01673950530140193</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0">
-        <v>252.64767176017193</v>
+        <v>325.53436131516344</v>
       </c>
       <c r="B214" s="0">
-        <v>45.874048031436132</v>
+        <v>2.7881429618278277</v>
       </c>
       <c r="C214" s="0">
-        <v>34.298785046274979</v>
+        <v>0.39126864322358629</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0">
-        <v>253.22851812795156</v>
+        <v>326.17401315664097</v>
       </c>
       <c r="B215" s="0">
-        <v>45.874048031436132</v>
+        <v>2.8953309645444132</v>
       </c>
       <c r="C215" s="0">
-        <v>34.298785046274979</v>
+        <v>0.23968191605810696</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0">
-        <v>253.80936449573119</v>
+        <v>326.81366499811844</v>
       </c>
       <c r="B216" s="0">
-        <v>45.874048031436132</v>
+        <v>2.6236848879997989</v>
       </c>
       <c r="C216" s="0">
-        <v>34.298785046274979</v>
+        <v>0.023424820202337948</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0">
-        <v>254.39021086351085</v>
+        <v>327.45331683959591</v>
       </c>
       <c r="B217" s="0">
-        <v>51.924115570228544</v>
+        <v>2.8245622147354457</v>
       </c>
       <c r="C217" s="0">
-        <v>25.742697479641535</v>
+        <v>0.031963635618679341</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0">
-        <v>254.97105723129044</v>
+        <v>328.09296868107344</v>
       </c>
       <c r="B218" s="0">
-        <v>51.924115570228544</v>
+        <v>2.7061420278473811</v>
       </c>
       <c r="C218" s="0">
-        <v>25.742697479641535</v>
+        <v>0.13550779873717842</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0">
-        <v>255.5519035990701</v>
+        <v>328.73262052255097</v>
       </c>
       <c r="B219" s="0">
-        <v>51.924115570228544</v>
+        <v>2.5343844573282928</v>
       </c>
       <c r="C219" s="0">
-        <v>25.742697479641535</v>
+        <v>0.10739408693116961</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0">
-        <v>256.1327499668497</v>
+        <v>329.37227236402845</v>
       </c>
       <c r="B220" s="0">
-        <v>51.924115570228544</v>
+        <v>2.6211898049239215</v>
       </c>
       <c r="C220" s="0">
-        <v>25.742697479641535</v>
+        <v>0.23015538678741882</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0">
-        <v>256.71359633462936</v>
+        <v>330.01192420550592</v>
       </c>
       <c r="B221" s="0">
-        <v>51.924115570228544</v>
+        <v>2.4961550983606826</v>
       </c>
       <c r="C221" s="0">
-        <v>25.742697479641535</v>
+        <v>0.05332960899834583</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0">
-        <v>257.29444270240902</v>
+        <v>330.65157604698345</v>
       </c>
       <c r="B222" s="0">
-        <v>51.924115570228544</v>
+        <v>2.6669623948234182</v>
       </c>
       <c r="C222" s="0">
-        <v>25.742697479641535</v>
+        <v>0.081813545788454817</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0">
-        <v>257.87528907018861</v>
+        <v>331.29122788846092</v>
       </c>
       <c r="B223" s="0">
-        <v>51.924115570228544</v>
+        <v>2.4488750177274228</v>
       </c>
       <c r="C223" s="0">
-        <v>25.742697479641535</v>
+        <v>0.076948910086801131</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0">
-        <v>258.45613543796827</v>
+        <v>331.9308797299384</v>
       </c>
       <c r="B224" s="0">
-        <v>51.924115570228544</v>
+        <v>2.484384874101405</v>
       </c>
       <c r="C224" s="0">
-        <v>25.742697479641535</v>
+        <v>0.02673038960479451</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0">
-        <v>259.03698180574793</v>
+        <v>332.57053157141593</v>
       </c>
       <c r="B225" s="0">
-        <v>51.924115570228544</v>
+        <v>2.5993598603609436</v>
       </c>
       <c r="C225" s="0">
-        <v>25.742697479641535</v>
+        <v>0.18932957450669397</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0">
-        <v>259.61782817352753</v>
+        <v>333.2101834128934</v>
       </c>
       <c r="B226" s="0">
-        <v>51.924115570228544</v>
+        <v>2.5993598603609436</v>
       </c>
       <c r="C226" s="0">
-        <v>25.742697479641535</v>
+        <v>0.18932957450669397</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0">
-        <v>260.19867454130713</v>
+        <v>333.84983525437087</v>
       </c>
       <c r="B227" s="0">
-        <v>51.924115570228544</v>
+        <v>2.5468419031837133</v>
       </c>
       <c r="C227" s="0">
-        <v>25.742697479641535</v>
+        <v>0.11505796719852576</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0">
-        <v>260.77952090908678</v>
+        <v>334.4894870958484</v>
       </c>
       <c r="B228" s="0">
-        <v>51.924115570228544</v>
+        <v>2.3832067191710298</v>
       </c>
       <c r="C228" s="0">
-        <v>25.742697479641535</v>
+        <v>0.34647306371068015</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0">
-        <v>261.36036727686644</v>
+        <v>335.12913893732593</v>
       </c>
       <c r="B229" s="0">
-        <v>51.924115570228544</v>
+        <v>2.4660041015229286</v>
       </c>
       <c r="C229" s="0">
-        <v>25.742697479641535</v>
+        <v>0.25377187701222836</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0">
-        <v>261.94121364464604</v>
+        <v>335.76879077880341</v>
       </c>
       <c r="B230" s="0">
-        <v>51.924115570228544</v>
+        <v>2.4660041015229286</v>
       </c>
       <c r="C230" s="0">
-        <v>25.742697479641535</v>
+        <v>0.25377187701222836</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0">
-        <v>262.5220600124257</v>
+        <v>336.40844262028088</v>
       </c>
       <c r="B231" s="0">
-        <v>51.924115570228544</v>
+        <v>2.4028752499710793</v>
       </c>
       <c r="C231" s="0">
-        <v>25.742697479641535</v>
+        <v>0.098895138238129787</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0">
-        <v>263.10290638020535</v>
+        <v>337.04809446175841</v>
       </c>
       <c r="B232" s="0">
-        <v>51.924115570228544</v>
+        <v>2.3081714151809547</v>
       </c>
       <c r="C232" s="0">
-        <v>25.742697479641535</v>
+        <v>0.13446348271150638</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0">
-        <v>263.68375274798496</v>
+        <v>337.68774630323594</v>
       </c>
       <c r="B233" s="0">
-        <v>51.924115570228544</v>
+        <v>2.3081714151809547</v>
       </c>
       <c r="C233" s="0">
-        <v>25.742697479641535</v>
+        <v>0.13446348271150638</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0">
-        <v>264.26459911576461</v>
+        <v>338.32739814471336</v>
       </c>
       <c r="B234" s="0">
-        <v>51.924115570228544</v>
+        <v>2.4143132941483976</v>
       </c>
       <c r="C234" s="0">
-        <v>25.742697479641535</v>
+        <v>0.015643802060014894</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0">
-        <v>264.84544548354421</v>
+        <v>338.96704998619089</v>
       </c>
       <c r="B235" s="0">
-        <v>51.924115570228544</v>
+        <v>2.3720867639191416</v>
       </c>
       <c r="C235" s="0">
-        <v>25.742697479641535</v>
+        <v>0.22702001206623232</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0">
-        <v>265.42629185132387</v>
+        <v>339.60670182766842</v>
       </c>
       <c r="B236" s="0">
-        <v>51.924115570228544</v>
+        <v>2.2888945752178262</v>
       </c>
       <c r="C236" s="0">
-        <v>25.742697479641535</v>
+        <v>0.00691188610251613</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0">
-        <v>266.00713821910347</v>
+        <v>340.24635366914595</v>
       </c>
       <c r="B237" s="0">
-        <v>51.924115570228544</v>
+        <v>2.2888945752178262</v>
       </c>
       <c r="C237" s="0">
-        <v>25.742697479641535</v>
+        <v>0.00691188610251613</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0">
-        <v>266.58798458688312</v>
+        <v>340.88600551062336</v>
       </c>
       <c r="B238" s="0">
-        <v>51.924115570228544</v>
+        <v>1.9184496415581198</v>
       </c>
       <c r="C238" s="0">
-        <v>25.742697479641535</v>
+        <v>0.13025855901414668</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0">
-        <v>267.16883095466278</v>
+        <v>341.52565735210089</v>
       </c>
       <c r="B239" s="0">
-        <v>51.924115570228544</v>
+        <v>2.0720068955232316</v>
       </c>
       <c r="C239" s="0">
-        <v>25.742697479641535</v>
+        <v>0.34742131017237776</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0">
-        <v>267.74967732244238</v>
+        <v>342.16530919357842</v>
       </c>
       <c r="B240" s="0">
-        <v>51.924115570228544</v>
+        <v>1.9998418087363243</v>
       </c>
       <c r="C240" s="0">
-        <v>25.742697479641535</v>
+        <v>0.40097569381447778</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0">
-        <v>268.33052369022209</v>
+        <v>342.80496103505584</v>
       </c>
       <c r="B241" s="0">
-        <v>51.924115570228544</v>
+        <v>1.9998418087363243</v>
       </c>
       <c r="C241" s="0">
-        <v>25.742697479641535</v>
+        <v>0.40097569381447778</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0">
-        <v>268.91137005800169</v>
+        <v>343.44461287653337</v>
       </c>
       <c r="B242" s="0">
-        <v>51.924115570228544</v>
+        <v>2.2432893500503326</v>
       </c>
       <c r="C242" s="0">
-        <v>25.742697479641535</v>
+        <v>0.056688879161822969</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0">
-        <v>269.49221642578129</v>
+        <v>344.0842647180109</v>
       </c>
       <c r="B243" s="0">
-        <v>51.924115570228544</v>
+        <v>2.4465652479561104</v>
       </c>
       <c r="C243" s="0">
-        <v>25.742697479641535</v>
+        <v>0.055401851011190419</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0">
-        <v>270.07306279356095</v>
+        <v>344.72391655948837</v>
       </c>
       <c r="B244" s="0">
-        <v>51.924115570228544</v>
+        <v>2.4055780870102135</v>
       </c>
       <c r="C244" s="0">
-        <v>25.742697479641535</v>
+        <v>0.11336644990404704</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0">
-        <v>270.65390916134061</v>
+        <v>345.36356840096585</v>
       </c>
       <c r="B245" s="0">
-        <v>54.962509731425172</v>
+        <v>2.316771758907008</v>
       </c>
       <c r="C245" s="0">
-        <v>30.039635710241029</v>
+        <v>0.23895756353215511</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0">
-        <v>271.23475552912021</v>
+        <v>346.00322024244338</v>
       </c>
       <c r="B246" s="0">
-        <v>54.962509731425172</v>
+        <v>2.0395359391168873</v>
       </c>
       <c r="C246" s="0">
-        <v>30.039635710241029</v>
+        <v>0.021821949916600806</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0">
-        <v>271.81560189689986</v>
+        <v>346.64287208392091</v>
       </c>
       <c r="B247" s="0">
-        <v>54.962509731425172</v>
+        <v>2.0395359391168873</v>
       </c>
       <c r="C247" s="0">
-        <v>30.039635710241029</v>
+        <v>0.021821949916600806</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0">
-        <v>272.39644826467946</v>
+        <v>347.28252392539838</v>
       </c>
       <c r="B248" s="0">
-        <v>54.962509731425172</v>
+        <v>2.0395359391168873</v>
       </c>
       <c r="C248" s="0">
-        <v>30.039635710241029</v>
+        <v>0.021821949916600806</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0">
-        <v>272.97729463245912</v>
+        <v>347.92217576687585</v>
       </c>
       <c r="B249" s="0">
-        <v>54.962509731425172</v>
+        <v>1.8519174181236464</v>
       </c>
       <c r="C249" s="0">
-        <v>30.039635710241029</v>
+        <v>0.18687808809715631</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0">
-        <v>273.55814100023872</v>
+        <v>348.56182760835338</v>
       </c>
       <c r="B250" s="0">
-        <v>54.962509731425172</v>
+        <v>1.6672495852500027</v>
       </c>
       <c r="C250" s="0">
-        <v>30.039635710241029</v>
+        <v>0.074281665686798615</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0">
-        <v>274.13898736801838</v>
+        <v>349.20147944983086</v>
       </c>
       <c r="B251" s="0">
-        <v>56.552113220783752</v>
+        <v>2.087314991844365</v>
       </c>
       <c r="C251" s="0">
-        <v>32.287674523687528</v>
+        <v>0.079999112332204775</v>
       </c>
     </row>
   </sheetData>
